--- a/llmserver/excelsheets/PAYOOR_PRODUCTS.xlsx
+++ b/llmserver/excelsheets/PAYOOR_PRODUCTS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="248">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="978" uniqueCount="373">
   <si>
     <t>NAME</t>
   </si>
@@ -56,12 +56,45 @@
     <t>Rice (short grain)</t>
   </si>
   <si>
+    <t>1 paint bucket (3.85KG)</t>
+  </si>
+  <si>
+    <t>Ofada rice - White</t>
+  </si>
+  <si>
+    <t>1 paint bucket (4kg)</t>
+  </si>
+  <si>
+    <t>Derica [600g]</t>
+  </si>
+  <si>
+    <t>Half paint [2kg]</t>
+  </si>
+  <si>
+    <t>Ofada rice - brown</t>
+  </si>
+  <si>
+    <t>Half paint(2kg)</t>
+  </si>
+  <si>
+    <t>Derica(600g)</t>
+  </si>
+  <si>
+    <t>Ofada rice (Abakaliki)</t>
+  </si>
+  <si>
     <t xml:space="preserve"> Basmati Rice - Tropical Sun Golden Stella </t>
   </si>
   <si>
     <t>5kg</t>
   </si>
   <si>
+    <t>2kg</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Basmati Rice - Tilda golden sella</t>
+  </si>
+  <si>
     <t>Beans - oloyin</t>
   </si>
   <si>
@@ -101,12 +134,6 @@
     <t>Chicken Lap - meat</t>
   </si>
   <si>
-    <t>4.5kg (half carton)</t>
-  </si>
-  <si>
-    <t>9kg (1 carton)</t>
-  </si>
-  <si>
     <t>Chicken wings - meat</t>
   </si>
   <si>
@@ -206,6 +233,15 @@
     <t>2.5Litres</t>
   </si>
   <si>
+    <t>1.4Litres</t>
+  </si>
+  <si>
+    <t>4.5Litres</t>
+  </si>
+  <si>
+    <t>750ml</t>
+  </si>
+  <si>
     <t>Palm Oil - Local</t>
   </si>
   <si>
@@ -275,25 +311,25 @@
     <t>6.25Kg (Quarter Basket)</t>
   </si>
   <si>
-    <t>12.5Kg (Half Basket)</t>
-  </si>
-  <si>
-    <t>25Kg (1 Basket )</t>
+    <t>12.5Kg (Half Bag)</t>
+  </si>
+  <si>
+    <t>25Kg (1 bag)</t>
   </si>
   <si>
     <t xml:space="preserve">Pepper - Tatase </t>
   </si>
   <si>
-    <t>1.7kg (paint bucket)</t>
-  </si>
-  <si>
-    <t>6.25kg (quarter basket)</t>
-  </si>
-  <si>
-    <t>12.5kg (half basket)</t>
-  </si>
-  <si>
-    <t>25kg (1 basket)</t>
+    <t>1.75kg (paint bag)</t>
+  </si>
+  <si>
+    <t>6.25kg (quarter bag)</t>
+  </si>
+  <si>
+    <t>12.5kg (half bag)</t>
+  </si>
+  <si>
+    <t>25kg (1 bag)</t>
   </si>
   <si>
     <t>Yam</t>
@@ -320,7 +356,7 @@
     <t>EGG</t>
   </si>
   <si>
-    <t xml:space="preserve">1 Crate </t>
+    <t>1 Crate (30)</t>
   </si>
   <si>
     <t>Onions - Red</t>
@@ -344,10 +380,10 @@
     <t>1 bag</t>
   </si>
   <si>
-    <t xml:space="preserve">Garri - 1jebu </t>
-  </si>
-  <si>
-    <t>1.75kg (1 Paint Bucket )</t>
+    <t>Garri - white</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garri - Ijebu </t>
   </si>
   <si>
     <t>Salt - Mr chef</t>
@@ -389,7 +425,7 @@
     <t>1 carton</t>
   </si>
   <si>
-    <t>Shrimp[frozen]</t>
+    <t>Shrimp</t>
   </si>
   <si>
     <t>170g -230g</t>
@@ -398,6 +434,9 @@
     <t>700g - 1000g</t>
   </si>
   <si>
+    <t>Prawn</t>
+  </si>
+  <si>
     <t xml:space="preserve">Green Apples </t>
   </si>
   <si>
@@ -410,10 +449,13 @@
     <t xml:space="preserve"> 1 Crate 30</t>
   </si>
   <si>
-    <t>Grape (Red seedless)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1 pack</t>
+    <t xml:space="preserve">Grape </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 pack ((Red foreign)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 pack (dark purple nigerian)</t>
   </si>
   <si>
     <t xml:space="preserve">Pineapple (Cotonou -ripe &amp; ready) </t>
@@ -431,6 +473,12 @@
     <t xml:space="preserve"> 1 bunch</t>
   </si>
   <si>
+    <t>Pineapple ( Bendel unripe)</t>
+  </si>
+  <si>
+    <t>Pineapple ( Bendel ripe)</t>
+  </si>
+  <si>
     <t>Banana  (Regular bunch -unripe)</t>
   </si>
   <si>
@@ -470,15 +518,24 @@
     <t xml:space="preserve">1 kilo </t>
   </si>
   <si>
+    <t xml:space="preserve">Black Amala Flour [Elubo] - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Half paint bucket </t>
+  </si>
+  <si>
     <t>Black Amala Flour [Elubo]</t>
   </si>
   <si>
-    <t xml:space="preserve">Half paint bucket </t>
-  </si>
-  <si>
     <t xml:space="preserve">Paint bucket </t>
   </si>
   <si>
+    <t>White Amala Flour [Elubo]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paint bucket </t>
+  </si>
+  <si>
     <t>Sweet Bell pepper mix [Green, red and yellow]</t>
   </si>
   <si>
@@ -707,7 +764,10 @@
     <t>Zobo leaf</t>
   </si>
   <si>
-    <t>100g</t>
+    <t>Derica</t>
+  </si>
+  <si>
+    <t>Zobo leaf - blended</t>
   </si>
   <si>
     <t>Sugar</t>
@@ -757,6 +817,321 @@
   </si>
   <si>
     <t>15g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cucumber </t>
+  </si>
+  <si>
+    <t>big(1)</t>
+  </si>
+  <si>
+    <t>big ( 3)</t>
+  </si>
+  <si>
+    <t>big (6)</t>
+  </si>
+  <si>
+    <t>Watermelon</t>
+  </si>
+  <si>
+    <t>medium(1)</t>
+  </si>
+  <si>
+    <t>Big(1)</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t xml:space="preserve">single </t>
+  </si>
+  <si>
+    <t>half basket(25)</t>
+  </si>
+  <si>
+    <t>full basket(50)</t>
+  </si>
+  <si>
+    <t>Avocado</t>
+  </si>
+  <si>
+    <t>Big (1)</t>
+  </si>
+  <si>
+    <t>Medium (1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garlic </t>
+  </si>
+  <si>
+    <t>Single Clove</t>
+  </si>
+  <si>
+    <t>1 Pack (10)</t>
+  </si>
+  <si>
+    <t>Potash</t>
+  </si>
+  <si>
+    <t>Alum</t>
+  </si>
+  <si>
+    <t>Tigernut</t>
+  </si>
+  <si>
+    <t>Milk Cup [150]</t>
+  </si>
+  <si>
+    <t>Derica [555g)</t>
+  </si>
+  <si>
+    <t>Paint bucket [3kg)</t>
+  </si>
+  <si>
+    <t>Half Paint bucket [1.5kg)</t>
+  </si>
+  <si>
+    <t>Spring Onion</t>
+  </si>
+  <si>
+    <t>Bitter leaf - Whole</t>
+  </si>
+  <si>
+    <t>200g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bitter leaf - chopped </t>
+  </si>
+  <si>
+    <t>Parsley leaf</t>
+  </si>
+  <si>
+    <t>50g</t>
+  </si>
+  <si>
+    <t>Broccoli</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Big</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payoor Suya pepper </t>
+  </si>
+  <si>
+    <t>150g</t>
+  </si>
+  <si>
+    <t>Sole Fish - Abo</t>
+  </si>
+  <si>
+    <t>Pack of 3</t>
+  </si>
+  <si>
+    <t>Sweet corn</t>
+  </si>
+  <si>
+    <t>PACK OF 4</t>
+  </si>
+  <si>
+    <t>Egg plant</t>
+  </si>
+  <si>
+    <t>500G</t>
+  </si>
+  <si>
+    <t>Chia Seed</t>
+  </si>
+  <si>
+    <t>Flour for baking</t>
+  </si>
+  <si>
+    <t>Half Paint [1kg]</t>
+  </si>
+  <si>
+    <t>Full Paint [2kg]</t>
+  </si>
+  <si>
+    <t>Agbalumo</t>
+  </si>
+  <si>
+    <t>Half basket(25)</t>
+  </si>
+  <si>
+    <t>Half basket(50)</t>
+  </si>
+  <si>
+    <t>Banga - Palm kernel fruit</t>
+  </si>
+  <si>
+    <t>Half paint [1.5kg]</t>
+  </si>
+  <si>
+    <t>Full paint [3kg]</t>
+  </si>
+  <si>
+    <t>Scent leaf</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>Scent leaf - chopped</t>
+  </si>
+  <si>
+    <t>40g</t>
+  </si>
+  <si>
+    <t>Lettuce</t>
+  </si>
+  <si>
+    <t>Ayoola poundo</t>
+  </si>
+  <si>
+    <t>450g</t>
+  </si>
+  <si>
+    <t>1.8KG</t>
+  </si>
+  <si>
+    <t>900KG</t>
+  </si>
+  <si>
+    <t>4.5KG</t>
+  </si>
+  <si>
+    <t>Poundo - Payoor Poundo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dish wash - Morning Fresh </t>
+  </si>
+  <si>
+    <t>Simply pasta</t>
+  </si>
+  <si>
+    <t>Indomie Noodle - onion</t>
+  </si>
+  <si>
+    <t>70g</t>
+  </si>
+  <si>
+    <t>120g</t>
+  </si>
+  <si>
+    <t>Carton [70g x 40]</t>
+  </si>
+  <si>
+    <t>Carton [120g x 40]</t>
+  </si>
+  <si>
+    <t>Indomie Noodle - Chicken Peppersoup</t>
+  </si>
+  <si>
+    <t>100g</t>
+  </si>
+  <si>
+    <t>Carton [100g x 40]</t>
+  </si>
+  <si>
+    <t>Honeywell Spaghetti</t>
+  </si>
+  <si>
+    <t>Indomie Noodle - original chicken</t>
+  </si>
+  <si>
+    <t>belleful</t>
+  </si>
+  <si>
+    <t>Carton [belleful}</t>
+  </si>
+  <si>
+    <t>Cadbury Bournvita</t>
+  </si>
+  <si>
+    <t>20g</t>
+  </si>
+  <si>
+    <t>900g</t>
+  </si>
+  <si>
+    <t>Hollandia Full Cream Evaporated</t>
+  </si>
+  <si>
+    <t>Carton[50g x 48]</t>
+  </si>
+  <si>
+    <t>Carton[120g x 48]</t>
+  </si>
+  <si>
+    <t>190g</t>
+  </si>
+  <si>
+    <t>Carton [190g x 24]</t>
+  </si>
+  <si>
+    <t>Lipton Yellow Label Tea</t>
+  </si>
+  <si>
+    <t>25 Tea Bag</t>
+  </si>
+  <si>
+    <t>Capri-sun -Apple</t>
+  </si>
+  <si>
+    <t>100ml</t>
+  </si>
+  <si>
+    <t>Cartoon [100ml x 40]</t>
+  </si>
+  <si>
+    <t>200ml</t>
+  </si>
+  <si>
+    <t>Carton [200ml x40]</t>
+  </si>
+  <si>
+    <t>Capri-sun -Orange</t>
+  </si>
+  <si>
+    <t>Capri-sun -orange</t>
+  </si>
+  <si>
+    <t>Capri-sun - orange</t>
+  </si>
+  <si>
+    <t>Titus Sardine</t>
+  </si>
+  <si>
+    <t>125g</t>
+  </si>
+  <si>
+    <t>A carton (125g X 5)</t>
+  </si>
+  <si>
+    <t>Nasco Cornflakes - Original</t>
+  </si>
+  <si>
+    <t>350g</t>
+  </si>
+  <si>
+    <t>Kellogg's Cornflakes</t>
+  </si>
+  <si>
+    <t>300G</t>
+  </si>
+  <si>
+    <t>1kG</t>
+  </si>
+  <si>
+    <t>Water yam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Small Tuber </t>
+  </si>
+  <si>
+    <t>Big Tuber</t>
   </si>
 </sst>
 </file>
@@ -945,10 +1320,10 @@
         <color rgb="FF284E3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -956,13 +1331,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -970,13 +1345,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -986,7 +1361,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="52">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1023,6 +1398,9 @@
     <xf borderId="9" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -1041,7 +1419,16 @@
     <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1050,11 +1437,23 @@
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1065,10 +1464,13 @@
     <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="9" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="9" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1077,23 +1479,32 @@
     <xf borderId="5" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="8" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="5" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="2" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
@@ -1169,7 +1580,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F1170" displayName="Table1" name="Table1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F1193" displayName="Table1" name="Table1" id="1">
   <tableColumns count="6">
     <tableColumn name="NAME" id="1"/>
     <tableColumn name="UNIT" id="2"/>
@@ -1414,7 +1825,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="5">
-        <v>1919.0</v>
+        <v>2630.0</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>8</v>
@@ -1430,7 +1841,7 @@
         <v>9</v>
       </c>
       <c r="C3" s="9">
-        <v>4960.0</v>
+        <v>7025.0</v>
       </c>
       <c r="D3" s="9" t="s">
         <v>8</v>
@@ -1445,8 +1856,8 @@
       <c r="B4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="5">
-        <v>9919.0</v>
+      <c r="C4" s="12">
+        <v>14050.0</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>8</v>
@@ -1462,7 +1873,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="9">
-        <v>50149.0</v>
+        <v>88150.0</v>
       </c>
       <c r="D5" s="9" t="s">
         <v>8</v>
@@ -1478,7 +1889,7 @@
         <v>12</v>
       </c>
       <c r="C6" s="5">
-        <v>100199.0</v>
+        <v>176300.0</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>8</v>
@@ -1487,254 +1898,254 @@
       <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="14">
-        <v>1919.0</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="C7" s="15">
+        <v>1250.0</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E7" s="10"/>
       <c r="F7" s="11"/>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="17">
-        <v>4960.0</v>
-      </c>
-      <c r="D8" s="16" t="s">
+      <c r="C8" s="18">
+        <v>3675.0</v>
+      </c>
+      <c r="D8" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="7"/>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="C9" s="14">
-        <v>9919.0</v>
-      </c>
-      <c r="D9" s="13" t="s">
+      <c r="B9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9" s="19">
+        <v>7350.0</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E9" s="10"/>
       <c r="F9" s="11"/>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="17">
-        <v>50149.0</v>
-      </c>
-      <c r="D10" s="16" t="s">
+      <c r="C10" s="18">
+        <v>46900.0</v>
+      </c>
+      <c r="D10" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="7"/>
     </row>
     <row r="11">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="14">
-        <v>100199.0</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="C11" s="15">
+        <v>93800.0</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="11"/>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="14">
-        <v>25199.0</v>
-      </c>
-      <c r="D12" s="14" t="s">
+      <c r="B12" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="15">
+        <v>19500.0</v>
+      </c>
+      <c r="D12" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="7"/>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="9" t="s">
+      <c r="A13" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="9">
-        <v>154099.0</v>
-      </c>
-      <c r="D13" s="9" t="s">
+      <c r="C13" s="21">
+        <v>2950.0</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E13" s="10"/>
       <c r="F13" s="11"/>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="17">
-        <v>1959.0</v>
-      </c>
-      <c r="D14" s="16" t="s">
+      <c r="C14" s="21">
+        <v>9800.0</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="7"/>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="s">
+      <c r="A15" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="14">
-        <v>5969.0</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="10"/>
+      <c r="B15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="21">
+        <v>17500.0</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="22"/>
       <c r="F15" s="11"/>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="17">
-        <v>11729.0</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E16" s="6"/>
+      <c r="C16" s="25">
+        <v>8750.0</v>
+      </c>
+      <c r="D16" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="22"/>
       <c r="F16" s="7"/>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="s">
+      <c r="A17" s="23" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="14">
-        <v>144299.0</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E17" s="10"/>
+      <c r="C17" s="25">
+        <v>2659.0</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="27"/>
       <c r="F17" s="11"/>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="s">
-        <v>19</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C18" s="17">
-        <v>288499.0</v>
-      </c>
-      <c r="D18" s="16" t="s">
+      <c r="A18" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="15">
+        <v>13500.0</v>
+      </c>
+      <c r="D18" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E18" s="6"/>
       <c r="F18" s="7"/>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="s">
-        <v>22</v>
-      </c>
-      <c r="B19" s="9" t="s">
+      <c r="A19" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="9">
-        <v>3150.0</v>
-      </c>
-      <c r="D19" s="9" t="s">
+      <c r="B19" s="29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C19" s="29">
+        <v>25199.0</v>
+      </c>
+      <c r="D19" s="29" t="s">
         <v>8</v>
       </c>
       <c r="E19" s="10"/>
       <c r="F19" s="11"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C20" s="5">
-        <v>6300.0</v>
-      </c>
-      <c r="D20" s="5" t="s">
+      <c r="A20" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C20" s="15">
+        <v>10700.0</v>
+      </c>
+      <c r="D20" s="15" t="s">
         <v>8</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="7"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="C21" s="9">
-        <v>28700.0</v>
-      </c>
-      <c r="D21" s="9" t="s">
+      <c r="A21" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21" s="21">
+        <v>33450.0</v>
+      </c>
+      <c r="D21" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E21" s="10"/>
       <c r="F21" s="11"/>
     </row>
     <row r="22">
-      <c r="A22" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B22" s="20" t="s">
-        <v>26</v>
+      <c r="A22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>28</v>
       </c>
       <c r="C22" s="5">
-        <v>57500.0</v>
+        <v>154099.0</v>
       </c>
       <c r="D22" s="5" t="s">
         <v>8</v>
@@ -1743,382 +2154,382 @@
       <c r="F22" s="7"/>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" s="17">
-        <v>3610.0</v>
-      </c>
-      <c r="D23" s="16" t="s">
+      <c r="A23" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="18">
+        <v>1959.0</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E23" s="10"/>
       <c r="F23" s="11"/>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="14">
-        <v>7120.0</v>
-      </c>
-      <c r="D24" s="13" t="s">
+      <c r="A24" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="15">
+        <v>5969.0</v>
+      </c>
+      <c r="D24" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="7"/>
     </row>
     <row r="25">
-      <c r="A25" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="B25" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="C25" s="17">
-        <v>29230.0</v>
-      </c>
-      <c r="D25" s="16" t="s">
+      <c r="A25" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="18">
+        <v>11729.0</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E25" s="10"/>
       <c r="F25" s="11"/>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B26" s="13" t="s">
+      <c r="A26" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C26" s="14">
-        <v>58450.0</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="B26" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="15">
+        <v>144299.0</v>
+      </c>
+      <c r="D26" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="C27" s="14">
-        <v>6500.0</v>
-      </c>
-      <c r="D27" s="13" t="s">
+      <c r="A27" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="18">
+        <v>288499.0</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E27" s="10"/>
       <c r="F27" s="11"/>
     </row>
     <row r="28">
-      <c r="A28" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="C28" s="17">
-        <v>32440.0</v>
-      </c>
-      <c r="D28" s="16" t="s">
+      <c r="A28" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C28" s="5">
+        <v>3150.0</v>
+      </c>
+      <c r="D28" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E28" s="6"/>
       <c r="F28" s="7"/>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="C29" s="14">
-        <v>64790.0</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="A29" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C29" s="9">
+        <v>6300.0</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E29" s="10"/>
       <c r="F29" s="11"/>
     </row>
     <row r="30">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="C30" s="17">
-        <v>5249.0</v>
-      </c>
-      <c r="D30" s="16" t="s">
+      <c r="B30" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" s="5">
+        <v>30750.0</v>
+      </c>
+      <c r="D30" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="7"/>
     </row>
     <row r="31">
-      <c r="A31" s="24" t="s">
+      <c r="A31" s="23" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="25" t="s">
-        <v>24</v>
-      </c>
-      <c r="C31" s="26">
-        <v>10200.0</v>
-      </c>
-      <c r="D31" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E31" s="27"/>
-      <c r="F31" s="28"/>
+      <c r="B31" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" s="9">
+        <v>61500.0</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="10"/>
+      <c r="F31" s="11"/>
     </row>
     <row r="32">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="B32" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="20" t="s">
+      <c r="C32" s="18">
+        <v>3610.0</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="B33" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="20">
-        <v>110039.0</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="29"/>
-      <c r="F32" s="30"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="15" t="s">
+      <c r="C33" s="15">
+        <v>6300.0</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="10"/>
+      <c r="F33" s="11"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="17">
-        <v>116039.0</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="31"/>
-      <c r="F33" s="28"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C34" s="5">
-        <v>3539.0</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>39</v>
+      <c r="C34" s="18">
+        <v>30750.0</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>8</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="7"/>
     </row>
     <row r="35">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="17">
-        <v>33649.0</v>
-      </c>
-      <c r="D35" s="16" t="s">
-        <v>39</v>
+      <c r="C35" s="15">
+        <v>61500.0</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="E35" s="10"/>
       <c r="F35" s="11"/>
     </row>
     <row r="36">
-      <c r="A36" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="17">
-        <v>67199.0</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>39</v>
+      <c r="A36" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C36" s="15">
+        <v>6800.0</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="E36" s="6"/>
       <c r="F36" s="7"/>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="C37" s="9">
-        <v>6530.0</v>
-      </c>
-      <c r="D37" s="9" t="s">
+      <c r="A37" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>36</v>
+      </c>
+      <c r="C37" s="18">
+        <v>39000.0</v>
+      </c>
+      <c r="D37" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E37" s="10"/>
       <c r="F37" s="11"/>
     </row>
     <row r="38">
-      <c r="A38" s="18" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="C38" s="14">
-        <v>32269.0</v>
-      </c>
-      <c r="D38" s="13" t="s">
+      <c r="A38" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" s="15">
+        <v>68000.0</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="7"/>
     </row>
     <row r="39">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="31" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C39" s="14">
-        <v>64450.0</v>
-      </c>
-      <c r="D39" s="13" t="s">
+      <c r="B39" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="18">
+        <v>5249.0</v>
+      </c>
+      <c r="D39" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E39" s="10"/>
       <c r="F39" s="11"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="s">
+      <c r="A40" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B40" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="29">
+        <v>10200.0</v>
+      </c>
+      <c r="D40" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="34"/>
+      <c r="F40" s="35"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="18">
+        <v>110039.0</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="36"/>
+      <c r="F41" s="37"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="30" t="s">
         <v>45</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" s="5">
-        <v>4009.0</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="6"/>
-      <c r="F40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="17">
-        <v>19139.0</v>
-      </c>
-      <c r="D41" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="11"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="24" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="26">
-        <v>38000.0</v>
-      </c>
-      <c r="D42" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="6"/>
-      <c r="F42" s="7"/>
+      <c r="B42" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="24">
+        <v>116039.0</v>
+      </c>
+      <c r="D42" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="38"/>
+      <c r="F42" s="35"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="C43" s="9">
-        <v>3000.0</v>
+        <v>3539.0</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E43" s="10"/>
       <c r="F43" s="11"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="5">
-        <v>5300.0</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>8</v>
+      <c r="A44" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C44" s="18">
+        <v>33649.0</v>
+      </c>
+      <c r="D44" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="7"/>
     </row>
     <row r="45">
-      <c r="A45" s="8" t="s">
+      <c r="A45" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="B45" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C45" s="9">
-        <v>26500.0</v>
-      </c>
-      <c r="D45" s="9" t="s">
-        <v>8</v>
+      <c r="C45" s="18">
+        <v>67199.0</v>
+      </c>
+      <c r="D45" s="17" t="s">
+        <v>48</v>
       </c>
       <c r="E45" s="10"/>
       <c r="F45" s="11"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C46" s="5">
-        <v>53041.0</v>
+        <v>6530.0</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>8</v>
@@ -2127,46 +2538,46 @@
       <c r="F46" s="7"/>
     </row>
     <row r="47">
-      <c r="A47" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C47" s="9">
-        <v>900.0</v>
-      </c>
-      <c r="D47" s="9" t="s">
-        <v>39</v>
+      <c r="A47" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="C47" s="15">
+        <v>32269.0</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="E47" s="10"/>
       <c r="F47" s="11"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="s">
+      <c r="A48" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B48" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" s="5">
-        <v>2550.0</v>
-      </c>
-      <c r="D48" s="5" t="s">
-        <v>39</v>
+      <c r="C48" s="15">
+        <v>64450.0</v>
+      </c>
+      <c r="D48" s="14" t="s">
+        <v>8</v>
       </c>
       <c r="E48" s="6"/>
       <c r="F48" s="7"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C49" s="9">
-        <v>12300.0</v>
+        <v>4009.0</v>
       </c>
       <c r="D49" s="9" t="s">
         <v>8</v>
@@ -2175,32 +2586,32 @@
       <c r="F49" s="11"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C50" s="5">
-        <v>9999.0</v>
-      </c>
-      <c r="D50" s="5" t="s">
+      <c r="A50" s="31" t="s">
+        <v>54</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="18">
+        <v>19139.0</v>
+      </c>
+      <c r="D50" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E50" s="6"/>
       <c r="F50" s="7"/>
     </row>
     <row r="51">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B51" s="29" t="s">
         <v>57</v>
       </c>
-      <c r="B51" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C51" s="17">
-        <v>22100.0</v>
-      </c>
-      <c r="D51" s="16" t="s">
+      <c r="C51" s="29">
+        <v>38000.0</v>
+      </c>
+      <c r="D51" s="33" t="s">
         <v>8</v>
       </c>
       <c r="E51" s="10"/>
@@ -2208,13 +2619,13 @@
     </row>
     <row r="52">
       <c r="A52" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="C52" s="5">
-        <v>44379.0</v>
+        <v>3000.0</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>8</v>
@@ -2224,13 +2635,13 @@
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="C53" s="9">
-        <v>105559.0</v>
+        <v>5300.0</v>
       </c>
       <c r="D53" s="9" t="s">
         <v>8</v>
@@ -2240,13 +2651,13 @@
     </row>
     <row r="54">
       <c r="A54" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C54" s="5">
-        <v>11500.0</v>
+        <v>26500.0</v>
       </c>
       <c r="D54" s="5" t="s">
         <v>8</v>
@@ -2256,13 +2667,13 @@
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C55" s="9">
-        <v>2269.0</v>
+        <v>53000.0</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>8</v>
@@ -2272,45 +2683,45 @@
     </row>
     <row r="56">
       <c r="A56" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>63</v>
       </c>
       <c r="C56" s="5">
-        <v>5219.0</v>
+        <v>900.0</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E56" s="6"/>
       <c r="F56" s="7"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="B57" s="9" t="s">
-        <v>59</v>
-      </c>
       <c r="C57" s="9">
-        <v>10279.0</v>
+        <v>2550.0</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E57" s="10"/>
       <c r="F57" s="11"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C58" s="5">
-        <v>649.0</v>
+        <v>12300.0</v>
       </c>
       <c r="D58" s="5" t="s">
         <v>8</v>
@@ -2323,10 +2734,10 @@
         <v>66</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C59" s="9">
-        <v>1199.0</v>
+        <v>9500.0</v>
       </c>
       <c r="D59" s="9" t="s">
         <v>8</v>
@@ -2335,16 +2746,16 @@
       <c r="F59" s="11"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="s">
+      <c r="A60" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="5">
-        <v>3450.0</v>
-      </c>
-      <c r="D60" s="5" t="s">
+      <c r="B60" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="18">
+        <v>22950.0</v>
+      </c>
+      <c r="D60" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E60" s="6"/>
@@ -2355,10 +2766,10 @@
         <v>66</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C61" s="9">
-        <v>13849.0</v>
+        <v>69</v>
+      </c>
+      <c r="C61" s="39">
+        <v>47750.0</v>
       </c>
       <c r="D61" s="9" t="s">
         <v>8</v>
@@ -2371,10 +2782,10 @@
         <v>66</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C62" s="5">
-        <v>27599.0</v>
+        <v>105559.0</v>
       </c>
       <c r="D62" s="5" t="s">
         <v>8</v>
@@ -2384,13 +2795,13 @@
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B63" s="9" t="s">
         <v>72</v>
       </c>
       <c r="C63" s="9">
-        <v>55099.0</v>
+        <v>14000.0</v>
       </c>
       <c r="D63" s="9" t="s">
         <v>8</v>
@@ -2400,13 +2811,13 @@
     </row>
     <row r="64">
       <c r="A64" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="B64" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="5" t="s">
-        <v>74</v>
-      </c>
       <c r="C64" s="5">
-        <v>300.0</v>
+        <v>7600.0</v>
       </c>
       <c r="D64" s="5" t="s">
         <v>8</v>
@@ -2416,13 +2827,13 @@
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C65" s="9">
-        <v>1250.0</v>
+        <v>24400.0</v>
       </c>
       <c r="D65" s="9" t="s">
         <v>8</v>
@@ -2431,16 +2842,16 @@
       <c r="F65" s="11"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="C66" s="5">
-        <v>10519.0</v>
-      </c>
-      <c r="D66" s="5" t="s">
+      <c r="A66" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C66" s="40">
+        <v>4000.0</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E66" s="6"/>
@@ -2448,13 +2859,13 @@
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="B67" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="B67" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="C67" s="9">
-        <v>300.0</v>
+        <v>2269.0</v>
       </c>
       <c r="D67" s="9" t="s">
         <v>8</v>
@@ -2464,13 +2875,13 @@
     </row>
     <row r="68">
       <c r="A68" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C68" s="5">
-        <v>1250.0</v>
+        <v>5219.0</v>
       </c>
       <c r="D68" s="5" t="s">
         <v>8</v>
@@ -2480,13 +2891,13 @@
     </row>
     <row r="69">
       <c r="A69" s="8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="C69" s="9">
-        <v>10519.0</v>
+        <v>10279.0</v>
       </c>
       <c r="D69" s="9" t="s">
         <v>8</v>
@@ -2496,13 +2907,13 @@
     </row>
     <row r="70">
       <c r="A70" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>80</v>
-      </c>
       <c r="C70" s="5">
-        <v>1200.0</v>
+        <v>649.0</v>
       </c>
       <c r="D70" s="5" t="s">
         <v>8</v>
@@ -2512,13 +2923,13 @@
     </row>
     <row r="71">
       <c r="A71" s="8" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B71" s="9" t="s">
         <v>80</v>
       </c>
       <c r="C71" s="9">
-        <v>995.0</v>
+        <v>1199.0</v>
       </c>
       <c r="D71" s="9" t="s">
         <v>8</v>
@@ -2528,13 +2939,13 @@
     </row>
     <row r="72">
       <c r="A72" s="4" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C72" s="5">
-        <v>995.0</v>
+        <v>3450.0</v>
       </c>
       <c r="D72" s="5" t="s">
         <v>8</v>
@@ -2544,13 +2955,13 @@
     </row>
     <row r="73">
       <c r="A73" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C73" s="9">
-        <v>669.0</v>
+        <v>13849.0</v>
       </c>
       <c r="D73" s="9" t="s">
         <v>8</v>
@@ -2560,13 +2971,13 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="B74" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>67</v>
-      </c>
       <c r="C74" s="5">
-        <v>1200.0</v>
+        <v>27599.0</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>8</v>
@@ -2576,13 +2987,13 @@
     </row>
     <row r="75">
       <c r="A75" s="8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B75" s="9" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C75" s="9">
-        <v>2400.0</v>
+        <v>55099.0</v>
       </c>
       <c r="D75" s="9" t="s">
         <v>8</v>
@@ -2592,13 +3003,13 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C76" s="5">
-        <v>4000.0</v>
+        <v>300.0</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>8</v>
@@ -2608,13 +3019,13 @@
     </row>
     <row r="77">
       <c r="A77" s="8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B77" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C77" s="9">
-        <v>14200.0</v>
+        <v>1250.0</v>
       </c>
       <c r="D77" s="9" t="s">
         <v>8</v>
@@ -2623,46 +3034,46 @@
       <c r="F77" s="11"/>
     </row>
     <row r="78">
-      <c r="A78" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C78" s="14">
-        <v>28359.0</v>
-      </c>
-      <c r="D78" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E78" s="32"/>
+      <c r="A78" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="C78" s="5">
+        <v>10519.0</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="6"/>
       <c r="F78" s="7"/>
     </row>
     <row r="79">
-      <c r="A79" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B79" s="20" t="s">
-        <v>88</v>
-      </c>
-      <c r="C79" s="20">
-        <v>56349.0</v>
-      </c>
-      <c r="D79" s="22" t="s">
-        <v>8</v>
-      </c>
-      <c r="E79" s="33"/>
+      <c r="A79" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="C79" s="9">
+        <v>300.0</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E79" s="10"/>
       <c r="F79" s="11"/>
     </row>
     <row r="80">
       <c r="A80" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C80" s="5">
-        <v>919.0</v>
+        <v>1250.0</v>
       </c>
       <c r="D80" s="5" t="s">
         <v>8</v>
@@ -2672,13 +3083,13 @@
     </row>
     <row r="81">
       <c r="A81" s="8" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>67</v>
+        <v>88</v>
       </c>
       <c r="C81" s="9">
-        <v>1800.0</v>
+        <v>10519.0</v>
       </c>
       <c r="D81" s="9" t="s">
         <v>8</v>
@@ -2688,13 +3099,13 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="C82" s="5">
-        <v>3500.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D82" s="5" t="s">
         <v>8</v>
@@ -2704,13 +3115,13 @@
     </row>
     <row r="83">
       <c r="A83" s="8" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C83" s="9">
-        <v>5650.0</v>
+        <v>995.0</v>
       </c>
       <c r="D83" s="9" t="s">
         <v>8</v>
@@ -2720,13 +3131,13 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C84" s="5">
-        <v>20500.0</v>
+        <v>995.0</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>8</v>
@@ -2736,13 +3147,13 @@
     </row>
     <row r="85">
       <c r="A85" s="8" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="C85" s="9">
-        <v>40760.0</v>
+        <v>669.0</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>8</v>
@@ -2752,13 +3163,13 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="C86" s="5">
-        <v>81500.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>8</v>
@@ -2768,13 +3179,13 @@
     </row>
     <row r="87">
       <c r="A87" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="C87" s="9">
-        <v>2989.0</v>
+        <v>2400.0</v>
       </c>
       <c r="D87" s="9" t="s">
         <v>8</v>
@@ -2784,13 +3195,13 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C88" s="5">
-        <v>5100.0</v>
+        <v>4000.0</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>8</v>
@@ -2800,13 +3211,13 @@
     </row>
     <row r="89">
       <c r="A89" s="8" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C89" s="9">
-        <v>1260.0</v>
+        <v>15999.0</v>
       </c>
       <c r="D89" s="9" t="s">
         <v>8</v>
@@ -2815,46 +3226,46 @@
       <c r="F89" s="11"/>
     </row>
     <row r="90">
-      <c r="A90" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C90" s="5">
-        <v>2400.0</v>
-      </c>
-      <c r="D90" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E90" s="6"/>
+      <c r="A90" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="C90" s="15">
+        <v>31900.0</v>
+      </c>
+      <c r="D90" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="22"/>
       <c r="F90" s="7"/>
     </row>
     <row r="91">
-      <c r="A91" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="B91" s="9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C91" s="9">
-        <v>9100.0</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E91" s="10"/>
+      <c r="A91" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C91" s="24">
+        <v>64100.0</v>
+      </c>
+      <c r="D91" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="27"/>
       <c r="F91" s="11"/>
     </row>
     <row r="92">
       <c r="A92" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="C92" s="5">
-        <v>950.0</v>
+        <v>919.0</v>
       </c>
       <c r="D92" s="5" t="s">
         <v>8</v>
@@ -2864,13 +3275,13 @@
     </row>
     <row r="93">
       <c r="A93" s="8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="C93" s="9">
-        <v>2999.0</v>
+        <v>1800.0</v>
       </c>
       <c r="D93" s="9" t="s">
         <v>8</v>
@@ -2883,26 +3294,26 @@
         <v>101</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>102</v>
+        <v>47</v>
       </c>
       <c r="C94" s="5">
-        <v>7300.0</v>
+        <v>3200.0</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E94" s="6"/>
       <c r="F94" s="7"/>
     </row>
     <row r="95">
       <c r="A95" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B95" s="9" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C95" s="9">
-        <v>2199.0</v>
+        <v>5300.0</v>
       </c>
       <c r="D95" s="9" t="s">
         <v>8</v>
@@ -2912,13 +3323,13 @@
     </row>
     <row r="96">
       <c r="A96" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="B96" s="5" t="s">
-        <v>105</v>
-      </c>
       <c r="C96" s="5">
-        <v>7500.0</v>
+        <v>19000.0</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>8</v>
@@ -2928,13 +3339,13 @@
     </row>
     <row r="97">
       <c r="A97" s="8" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B97" s="9" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="C97" s="9">
-        <v>724.0</v>
+        <v>39000.0</v>
       </c>
       <c r="D97" s="9" t="s">
         <v>8</v>
@@ -2944,13 +3355,13 @@
     </row>
     <row r="98">
       <c r="A98" s="4" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C98" s="5">
-        <v>3100.0</v>
+        <v>78000.0</v>
       </c>
       <c r="D98" s="5" t="s">
         <v>8</v>
@@ -2963,10 +3374,10 @@
         <v>106</v>
       </c>
       <c r="B99" s="9" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C99" s="9">
-        <v>25678.0</v>
+        <v>3100.0</v>
       </c>
       <c r="D99" s="9" t="s">
         <v>8</v>
@@ -2979,10 +3390,10 @@
         <v>106</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C100" s="5">
-        <v>50699.0</v>
+        <v>5050.0</v>
       </c>
       <c r="D100" s="5" t="s">
         <v>8</v>
@@ -2992,13 +3403,13 @@
     </row>
     <row r="101">
       <c r="A101" s="8" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B101" s="9" t="s">
-        <v>111</v>
+        <v>79</v>
       </c>
       <c r="C101" s="9">
-        <v>3350.0</v>
+        <v>1260.0</v>
       </c>
       <c r="D101" s="9" t="s">
         <v>8</v>
@@ -3008,13 +3419,13 @@
     </row>
     <row r="102">
       <c r="A102" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>107</v>
+        <v>55</v>
       </c>
       <c r="C102" s="5">
-        <v>794.0</v>
+        <v>2700.0</v>
       </c>
       <c r="D102" s="5" t="s">
         <v>8</v>
@@ -3024,13 +3435,13 @@
     </row>
     <row r="103">
       <c r="A103" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B103" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="B103" s="9" t="s">
-        <v>69</v>
-      </c>
       <c r="C103" s="9">
-        <v>6909.0</v>
+        <v>9500.0</v>
       </c>
       <c r="D103" s="9" t="s">
         <v>8</v>
@@ -3040,13 +3451,13 @@
     </row>
     <row r="104">
       <c r="A104" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>108</v>
+        <v>47</v>
       </c>
       <c r="C104" s="5">
-        <v>51179.0</v>
+        <v>950.0</v>
       </c>
       <c r="D104" s="5" t="s">
         <v>8</v>
@@ -3056,13 +3467,13 @@
     </row>
     <row r="105">
       <c r="A105" s="8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B105" s="9" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C105" s="9">
-        <v>102249.0</v>
+        <v>2999.0</v>
       </c>
       <c r="D105" s="9" t="s">
         <v>8</v>
@@ -3072,29 +3483,29 @@
     </row>
     <row r="106">
       <c r="A106" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>38</v>
+        <v>114</v>
       </c>
       <c r="C106" s="5">
-        <v>569.0</v>
+        <v>6700.0</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E106" s="6"/>
       <c r="F106" s="7"/>
     </row>
     <row r="107">
       <c r="A107" s="8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B107" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C107" s="9">
-        <v>2730.0</v>
+        <v>2199.0</v>
       </c>
       <c r="D107" s="9" t="s">
         <v>8</v>
@@ -3107,10 +3518,10 @@
         <v>115</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C108" s="5">
-        <v>935.0</v>
+        <v>7500.0</v>
       </c>
       <c r="D108" s="5" t="s">
         <v>8</v>
@@ -3120,13 +3531,13 @@
     </row>
     <row r="109">
       <c r="A109" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B109" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C109" s="9">
-        <v>2730.0</v>
+        <v>724.0</v>
       </c>
       <c r="D109" s="9" t="s">
         <v>8</v>
@@ -3135,14 +3546,14 @@
       <c r="F109" s="11"/>
     </row>
     <row r="110">
-      <c r="A110" s="34" t="s">
-        <v>119</v>
+      <c r="A110" s="4" t="s">
+        <v>118</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C110" s="5">
-        <v>3500.0</v>
+        <v>3100.0</v>
       </c>
       <c r="D110" s="5" t="s">
         <v>8</v>
@@ -3151,96 +3562,96 @@
       <c r="F110" s="7"/>
     </row>
     <row r="111">
-      <c r="A111" s="35" t="s">
+      <c r="A111" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="9" t="s">
+        <v>120</v>
+      </c>
+      <c r="C111" s="9">
+        <v>25678.0</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E111" s="10"/>
+      <c r="F111" s="11"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C112" s="5">
+        <v>50699.0</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E112" s="6"/>
+      <c r="F112" s="7"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B113" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="B111" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="C111" s="14">
-        <v>9000.0</v>
-      </c>
-      <c r="D111" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E111" s="32"/>
-      <c r="F111" s="11"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="34" t="s">
-        <v>122</v>
-      </c>
-      <c r="B112" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C112" s="5">
-        <v>3500.0</v>
-      </c>
-      <c r="D112" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E112" s="32"/>
-      <c r="F112" s="7"/>
-    </row>
-    <row r="113">
-      <c r="A113" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="B113" s="9" t="s">
-        <v>124</v>
-      </c>
-      <c r="C113" s="9">
-        <v>11000.0</v>
-      </c>
-      <c r="D113" s="9" t="s">
+      <c r="C113" s="41">
+        <v>724.0</v>
+      </c>
+      <c r="D113" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E113" s="10"/>
       <c r="F113" s="11"/>
     </row>
     <row r="114">
-      <c r="A114" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="B114" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C114" s="5">
-        <v>3874.0</v>
-      </c>
-      <c r="D114" s="5" t="s">
+      <c r="A114" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="B114" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C114" s="42">
+        <v>3100.0</v>
+      </c>
+      <c r="D114" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E114" s="6"/>
       <c r="F114" s="7"/>
     </row>
     <row r="115">
-      <c r="A115" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="B115" s="9" t="s">
-        <v>127</v>
-      </c>
-      <c r="C115" s="9">
-        <v>15344.0</v>
-      </c>
-      <c r="D115" s="9" t="s">
+      <c r="A115" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="C115" s="41">
+        <v>25678.0</v>
+      </c>
+      <c r="D115" s="17" t="s">
         <v>8</v>
       </c>
       <c r="E115" s="10"/>
       <c r="F115" s="11"/>
     </row>
     <row r="116">
-      <c r="A116" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="B116" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="C116" s="5">
-        <v>510.0</v>
-      </c>
-      <c r="D116" s="5" t="s">
+      <c r="A116" s="20" t="s">
+        <v>118</v>
+      </c>
+      <c r="B116" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="C116" s="42">
+        <v>50699.0</v>
+      </c>
+      <c r="D116" s="14" t="s">
         <v>8</v>
       </c>
       <c r="E116" s="6"/>
@@ -3248,13 +3659,13 @@
     </row>
     <row r="117">
       <c r="A117" s="8" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B117" s="9" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="C117" s="9">
-        <v>6300.0</v>
+        <v>51179.0</v>
       </c>
       <c r="D117" s="9" t="s">
         <v>8</v>
@@ -3263,142 +3674,142 @@
       <c r="F117" s="11"/>
     </row>
     <row r="118">
-      <c r="A118" s="23" t="s">
+      <c r="A118" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C118" s="5">
+        <v>102249.0</v>
+      </c>
+      <c r="D118" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E118" s="6"/>
+      <c r="F118" s="7"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B119" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C119" s="9">
+        <v>600.0</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E119" s="10"/>
+      <c r="F119" s="11"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C120" s="5">
+        <v>2730.0</v>
+      </c>
+      <c r="D120" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E120" s="6"/>
+      <c r="F120" s="7"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="B121" s="9" t="s">
         <v>128</v>
       </c>
-      <c r="B118" s="17" t="s">
+      <c r="C121" s="9">
+        <v>935.0</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E121" s="10"/>
+      <c r="F121" s="11"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="C122" s="5">
+        <v>2730.0</v>
+      </c>
+      <c r="D122" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E122" s="6"/>
+      <c r="F122" s="7"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="C118" s="17">
-        <v>18000.0</v>
-      </c>
-      <c r="D118" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E118" s="31"/>
-      <c r="F118" s="7"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="15" t="s">
+      <c r="B123" s="9" t="s">
         <v>132</v>
       </c>
-      <c r="B119" s="17" t="s">
+      <c r="C123" s="9">
+        <v>3500.0</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="E123" s="10"/>
+      <c r="F123" s="11"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="44" t="s">
+        <v>131</v>
+      </c>
+      <c r="B124" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="C119" s="17">
-        <v>4650.0</v>
-      </c>
-      <c r="D119" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E119" s="31"/>
-      <c r="F119" s="11"/>
-    </row>
-    <row r="120">
-      <c r="A120" s="15" t="s">
+      <c r="C124" s="15">
+        <v>9000.0</v>
+      </c>
+      <c r="D124" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E124" s="22"/>
+      <c r="F124" s="7"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="43" t="s">
         <v>134</v>
       </c>
-      <c r="B120" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C120" s="17">
-        <v>1220.0</v>
-      </c>
-      <c r="D120" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E120" s="31"/>
-      <c r="F120" s="7"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="15" t="s">
-        <v>136</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C121" s="17">
-        <v>1220.0</v>
-      </c>
-      <c r="D121" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E121" s="31"/>
-      <c r="F121" s="11"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="C122" s="17">
-        <v>1200.0</v>
-      </c>
-      <c r="D122" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E122" s="31"/>
-      <c r="F122" s="7"/>
-    </row>
-    <row r="123">
-      <c r="A123" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="B123" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="C123" s="17">
-        <v>1200.0</v>
-      </c>
-      <c r="D123" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E123" s="31"/>
-      <c r="F123" s="11"/>
-    </row>
-    <row r="124">
-      <c r="A124" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B124" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C124" s="5">
-        <v>550.0</v>
-      </c>
-      <c r="D124" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E124" s="6"/>
-      <c r="F124" s="7"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="8" t="s">
-        <v>140</v>
-      </c>
       <c r="B125" s="9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C125" s="9">
-        <v>3529.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D125" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E125" s="10"/>
+      <c r="E125" s="27"/>
       <c r="F125" s="11"/>
     </row>
     <row r="126">
       <c r="A126" s="4" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="C126" s="5">
-        <v>7000.0</v>
+        <v>11000.0</v>
       </c>
       <c r="D126" s="5" t="s">
         <v>8</v>
@@ -3408,13 +3819,13 @@
     </row>
     <row r="127">
       <c r="A127" s="8" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B127" s="9" t="s">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="C127" s="9">
-        <v>1050.0</v>
+        <v>3860.0</v>
       </c>
       <c r="D127" s="9" t="s">
         <v>8</v>
@@ -3424,13 +3835,13 @@
     </row>
     <row r="128">
       <c r="A128" s="4" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C128" s="5">
-        <v>2100.0</v>
+        <v>15320.0</v>
       </c>
       <c r="D128" s="5" t="s">
         <v>8</v>
@@ -3440,13 +3851,13 @@
     </row>
     <row r="129">
       <c r="A129" s="8" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="B129" s="9" t="s">
-        <v>147</v>
-      </c>
-      <c r="C129" s="9">
-        <v>5200.0</v>
+        <v>79</v>
+      </c>
+      <c r="C129" s="39">
+        <v>10615.0</v>
       </c>
       <c r="D129" s="9" t="s">
         <v>8</v>
@@ -3455,30 +3866,30 @@
       <c r="F129" s="11"/>
     </row>
     <row r="130">
-      <c r="A130" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B130" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="C130" s="14">
-        <v>10550.0</v>
-      </c>
-      <c r="D130" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="E130" s="32"/>
+      <c r="A130" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="B130" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="C130" s="45">
+        <v>21198.0</v>
+      </c>
+      <c r="D130" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E130" s="6"/>
       <c r="F130" s="7"/>
     </row>
     <row r="131">
       <c r="A131" s="8" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B131" s="9" t="s">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="C131" s="9">
-        <v>420.0</v>
+        <v>510.0</v>
       </c>
       <c r="D131" s="9" t="s">
         <v>8</v>
@@ -3488,13 +3899,13 @@
     </row>
     <row r="132">
       <c r="A132" s="4" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="C132" s="5">
-        <v>840.0</v>
+        <v>6300.0</v>
       </c>
       <c r="D132" s="5" t="s">
         <v>8</v>
@@ -3503,176 +3914,176 @@
       <c r="F132" s="7"/>
     </row>
     <row r="133">
-      <c r="A133" s="8" t="s">
+      <c r="A133" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="B133" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C133" s="18">
+        <v>18000.0</v>
+      </c>
+      <c r="D133" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E133" s="36"/>
+      <c r="F133" s="11"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B134" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C134" s="18">
+        <v>4850.0</v>
+      </c>
+      <c r="D134" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E134" s="36"/>
+      <c r="F134" s="7"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="B135" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C135" s="18">
+        <v>4250.0</v>
+      </c>
+      <c r="D135" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E135" s="36"/>
+      <c r="F135" s="11"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="16" t="s">
+        <v>148</v>
+      </c>
+      <c r="B136" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B133" s="9" t="s">
+      <c r="C136" s="18">
+        <v>1220.0</v>
+      </c>
+      <c r="D136" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E136" s="36"/>
+      <c r="F136" s="7"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="16" t="s">
+        <v>150</v>
+      </c>
+      <c r="B137" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C137" s="18">
+        <v>1220.0</v>
+      </c>
+      <c r="D137" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E137" s="36"/>
+      <c r="F137" s="11"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="C133" s="9">
-        <v>1700.0</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E133" s="10"/>
-      <c r="F133" s="11"/>
-    </row>
-    <row r="134">
-      <c r="A134" s="4" t="s">
+      <c r="B138" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="B134" s="5" t="s">
+      <c r="C138" s="18">
+        <v>1200.0</v>
+      </c>
+      <c r="D138" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E138" s="36"/>
+      <c r="F138" s="7"/>
+    </row>
+    <row r="139">
+      <c r="A139" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="C134" s="5">
-        <v>3900.0</v>
-      </c>
-      <c r="D134" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E134" s="6"/>
-      <c r="F134" s="7"/>
-    </row>
-    <row r="135">
-      <c r="A135" s="8" t="s">
-        <v>152</v>
-      </c>
-      <c r="B135" s="9" t="s">
+      <c r="B139" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C139" s="18">
+        <v>1980.0</v>
+      </c>
+      <c r="D139" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E139" s="36"/>
+      <c r="F139" s="11"/>
+    </row>
+    <row r="140">
+      <c r="A140" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="C135" s="9">
-        <v>7800.0</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E135" s="10"/>
-      <c r="F135" s="11"/>
-    </row>
-    <row r="136">
-      <c r="A136" s="15" t="s">
+      <c r="B140" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C140" s="18">
+        <v>1980.0</v>
+      </c>
+      <c r="D140" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E140" s="36"/>
+      <c r="F140" s="7"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="16" t="s">
         <v>155</v>
       </c>
-      <c r="B136" s="17" t="s">
+      <c r="B141" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C141" s="18">
+        <v>1200.0</v>
+      </c>
+      <c r="D141" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E141" s="36"/>
+      <c r="F141" s="11"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C136" s="17">
-        <v>2900.0</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E136" s="6"/>
-      <c r="F136" s="7"/>
-    </row>
-    <row r="137">
-      <c r="A137" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="B137" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C137" s="17">
-        <v>5500.0</v>
-      </c>
-      <c r="D137" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="E137" s="31"/>
-      <c r="F137" s="11"/>
-    </row>
-    <row r="138">
-      <c r="A138" s="15" t="s">
+      <c r="B142" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="B138" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C138" s="17">
-        <v>2900.0</v>
-      </c>
-      <c r="D138" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E138" s="6"/>
-      <c r="F138" s="7"/>
-    </row>
-    <row r="139">
-      <c r="A139" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="B139" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C139" s="17">
-        <v>5500.0</v>
-      </c>
-      <c r="D139" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E139" s="10"/>
-      <c r="F139" s="11"/>
-    </row>
-    <row r="140">
-      <c r="A140" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B140" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C140" s="17">
-        <v>2900.0</v>
-      </c>
-      <c r="D140" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E140" s="6"/>
-      <c r="F140" s="7"/>
-    </row>
-    <row r="141">
-      <c r="A141" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="B141" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C141" s="17">
-        <v>5500.0</v>
-      </c>
-      <c r="D141" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="E141" s="10"/>
-      <c r="F141" s="11"/>
-    </row>
-    <row r="142">
-      <c r="A142" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B142" s="17" t="s">
-        <v>156</v>
-      </c>
-      <c r="C142" s="17">
-        <v>2900.0</v>
-      </c>
-      <c r="D142" s="17" t="s">
+      <c r="C142" s="5">
+        <v>550.0</v>
+      </c>
+      <c r="D142" s="5" t="s">
         <v>8</v>
       </c>
       <c r="E142" s="6"/>
       <c r="F142" s="7"/>
     </row>
     <row r="143">
-      <c r="A143" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="B143" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="C143" s="17">
-        <v>5500.0</v>
-      </c>
-      <c r="D143" s="17" t="s">
+      <c r="A143" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="C143" s="9">
+        <v>3529.0</v>
+      </c>
+      <c r="D143" s="9" t="s">
         <v>8</v>
       </c>
       <c r="E143" s="10"/>
@@ -3680,13 +4091,13 @@
     </row>
     <row r="144">
       <c r="A144" s="4" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C144" s="5">
-        <v>3550.0</v>
+        <v>7000.0</v>
       </c>
       <c r="D144" s="5" t="s">
         <v>8</v>
@@ -3699,10 +4110,10 @@
         <v>160</v>
       </c>
       <c r="B145" s="9" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C145" s="9">
-        <v>5210.0</v>
+        <v>1050.0</v>
       </c>
       <c r="D145" s="9" t="s">
         <v>8</v>
@@ -3715,10 +4126,10 @@
         <v>160</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C146" s="5">
-        <v>10420.0</v>
+        <v>2100.0</v>
       </c>
       <c r="D146" s="5" t="s">
         <v>8</v>
@@ -3728,13 +4139,13 @@
     </row>
     <row r="147">
       <c r="A147" s="8" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B147" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C147" s="9">
-        <v>3650.0</v>
+        <v>5200.0</v>
       </c>
       <c r="D147" s="9" t="s">
         <v>8</v>
@@ -3743,30 +4154,30 @@
       <c r="F147" s="11"/>
     </row>
     <row r="148">
-      <c r="A148" s="4" t="s">
+      <c r="A148" s="20" t="s">
+        <v>160</v>
+      </c>
+      <c r="B148" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="B148" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="C148" s="5">
-        <v>5350.0</v>
-      </c>
-      <c r="D148" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E148" s="6"/>
+      <c r="C148" s="15">
+        <v>10550.0</v>
+      </c>
+      <c r="D148" s="14" t="s">
+        <v>8</v>
+      </c>
+      <c r="E148" s="22"/>
       <c r="F148" s="7"/>
     </row>
     <row r="149">
       <c r="A149" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B149" s="9" t="s">
-        <v>167</v>
+        <v>96</v>
       </c>
       <c r="C149" s="9">
-        <v>820.0</v>
+        <v>420.0</v>
       </c>
       <c r="D149" s="9" t="s">
         <v>8</v>
@@ -3776,13 +4187,13 @@
     </row>
     <row r="150">
       <c r="A150" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B150" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="B150" s="5" t="s">
-        <v>168</v>
-      </c>
       <c r="C150" s="5">
-        <v>1490.0</v>
+        <v>840.0</v>
       </c>
       <c r="D150" s="5" t="s">
         <v>8</v>
@@ -3792,13 +4203,13 @@
     </row>
     <row r="151">
       <c r="A151" s="8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B151" s="9" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C151" s="9">
-        <v>2950.0</v>
+        <v>1700.0</v>
       </c>
       <c r="D151" s="9" t="s">
         <v>8</v>
@@ -3808,13 +4219,13 @@
     </row>
     <row r="152">
       <c r="A152" s="4" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C152" s="5">
-        <v>6810.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D152" s="5" t="s">
         <v>8</v>
@@ -3827,10 +4238,10 @@
         <v>170</v>
       </c>
       <c r="B153" s="9" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C153" s="9">
-        <v>3500.0</v>
+        <v>7000.0</v>
       </c>
       <c r="D153" s="9" t="s">
         <v>8</v>
@@ -3840,13 +4251,13 @@
     </row>
     <row r="154">
       <c r="A154" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>38</v>
+        <v>169</v>
       </c>
       <c r="C154" s="5">
-        <v>3200.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D154" s="5" t="s">
         <v>8</v>
@@ -3855,144 +4266,144 @@
       <c r="F154" s="7"/>
     </row>
     <row r="155">
-      <c r="A155" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="B155" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="C155" s="9">
-        <v>5385.0</v>
-      </c>
-      <c r="D155" s="9" t="s">
+      <c r="A155" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="B155" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C155" s="41">
+        <v>4000.0</v>
+      </c>
+      <c r="D155" s="46" t="s">
         <v>8</v>
       </c>
       <c r="E155" s="10"/>
       <c r="F155" s="11"/>
     </row>
     <row r="156">
-      <c r="A156" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="B156" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C156" s="5">
-        <v>2750.0</v>
-      </c>
-      <c r="D156" s="5" t="s">
+      <c r="A156" s="16" t="s">
+        <v>174</v>
+      </c>
+      <c r="B156" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C156" s="18">
+        <v>2900.0</v>
+      </c>
+      <c r="D156" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E156" s="6"/>
       <c r="F156" s="7"/>
     </row>
     <row r="157">
-      <c r="A157" s="8" t="s">
+      <c r="A157" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="B157" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C157" s="18">
+        <v>5500.0</v>
+      </c>
+      <c r="D157" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E157" s="36"/>
+      <c r="F157" s="11"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="B157" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="C157" s="9">
-        <v>4600.0</v>
-      </c>
-      <c r="D157" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="E157" s="10"/>
-      <c r="F157" s="11"/>
-    </row>
-    <row r="158">
-      <c r="A158" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C158" s="5">
-        <v>3860.0</v>
-      </c>
-      <c r="D158" s="5" t="s">
+      <c r="B158" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C158" s="18">
+        <v>2900.0</v>
+      </c>
+      <c r="D158" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E158" s="6"/>
       <c r="F158" s="7"/>
     </row>
     <row r="159">
-      <c r="A159" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="B159" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="C159" s="9">
-        <v>7700.0</v>
-      </c>
-      <c r="D159" s="9" t="s">
+      <c r="A159" s="16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B159" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C159" s="18">
+        <v>5500.0</v>
+      </c>
+      <c r="D159" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E159" s="10"/>
       <c r="F159" s="11"/>
     </row>
     <row r="160">
-      <c r="A160" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="B160" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="C160" s="5">
-        <v>8100.0</v>
-      </c>
-      <c r="D160" s="5" t="s">
+      <c r="A160" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B160" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C160" s="18">
+        <v>2900.0</v>
+      </c>
+      <c r="D160" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E160" s="6"/>
       <c r="F160" s="7"/>
     </row>
     <row r="161">
-      <c r="A161" s="8" t="s">
-        <v>181</v>
-      </c>
-      <c r="B161" s="9" t="s">
-        <v>182</v>
-      </c>
-      <c r="C161" s="9">
-        <v>3850.0</v>
-      </c>
-      <c r="D161" s="9" t="s">
+      <c r="A161" s="16" t="s">
+        <v>177</v>
+      </c>
+      <c r="B161" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C161" s="18">
+        <v>5500.0</v>
+      </c>
+      <c r="D161" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E161" s="10"/>
       <c r="F161" s="11"/>
     </row>
     <row r="162">
-      <c r="A162" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B162" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="C162" s="5">
-        <v>290.0</v>
-      </c>
-      <c r="D162" s="5" t="s">
+      <c r="A162" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B162" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C162" s="18">
+        <v>2900.0</v>
+      </c>
+      <c r="D162" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E162" s="6"/>
       <c r="F162" s="7"/>
     </row>
     <row r="163">
-      <c r="A163" s="8" t="s">
-        <v>183</v>
-      </c>
-      <c r="B163" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="C163" s="9">
-        <v>790.0</v>
-      </c>
-      <c r="D163" s="9" t="s">
+      <c r="A163" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="B163" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="C163" s="18">
+        <v>5500.0</v>
+      </c>
+      <c r="D163" s="18" t="s">
         <v>8</v>
       </c>
       <c r="E163" s="10"/>
@@ -4000,13 +4411,13 @@
     </row>
     <row r="164">
       <c r="A164" s="4" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B164" s="5" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C164" s="5">
-        <v>3600.0</v>
+        <v>3550.0</v>
       </c>
       <c r="D164" s="5" t="s">
         <v>8</v>
@@ -4016,13 +4427,13 @@
     </row>
     <row r="165">
       <c r="A165" s="8" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="B165" s="9" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="C165" s="9">
-        <v>3500.0</v>
+        <v>5210.0</v>
       </c>
       <c r="D165" s="9" t="s">
         <v>8</v>
@@ -4032,13 +4443,13 @@
     </row>
     <row r="166">
       <c r="A166" s="4" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B166" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C166" s="5">
-        <v>390.0</v>
+        <v>10420.0</v>
       </c>
       <c r="D166" s="5" t="s">
         <v>8</v>
@@ -4048,13 +4459,13 @@
     </row>
     <row r="167">
       <c r="A167" s="8" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B167" s="9" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C167" s="9">
-        <v>1805.0</v>
+        <v>3650.0</v>
       </c>
       <c r="D167" s="9" t="s">
         <v>8</v>
@@ -4064,13 +4475,13 @@
     </row>
     <row r="168">
       <c r="A168" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="B168" s="5" t="s">
-        <v>141</v>
+        <v>184</v>
       </c>
       <c r="C168" s="5">
-        <v>1200.0</v>
+        <v>5350.0</v>
       </c>
       <c r="D168" s="5" t="s">
         <v>8</v>
@@ -4080,13 +4491,13 @@
     </row>
     <row r="169">
       <c r="A169" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="B169" s="9" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C169" s="9">
-        <v>4360.0</v>
+        <v>820.0</v>
       </c>
       <c r="D169" s="9" t="s">
         <v>8</v>
@@ -4096,13 +4507,13 @@
     </row>
     <row r="170">
       <c r="A170" s="4" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B170" s="5" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C170" s="5">
-        <v>3500.0</v>
+        <v>1490.0</v>
       </c>
       <c r="D170" s="5" t="s">
         <v>8</v>
@@ -4112,109 +4523,109 @@
     </row>
     <row r="171">
       <c r="A171" s="8" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B171" s="9" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="C171" s="9">
-        <v>310.0</v>
+        <v>2950.0</v>
       </c>
       <c r="D171" s="9" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E171" s="10"/>
       <c r="F171" s="11"/>
     </row>
     <row r="172">
       <c r="A172" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B172" s="5" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C172" s="5">
-        <v>500.0</v>
+        <v>6810.0</v>
       </c>
       <c r="D172" s="5" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E172" s="6"/>
       <c r="F172" s="7"/>
     </row>
     <row r="173">
       <c r="A173" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B173" s="9" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="C173" s="9">
-        <v>795.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D173" s="9" t="s">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="E173" s="10"/>
       <c r="F173" s="11"/>
     </row>
     <row r="174">
       <c r="A174" s="4" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="B174" s="5" t="s">
-        <v>199</v>
+        <v>47</v>
       </c>
       <c r="C174" s="5">
-        <v>2000.0</v>
+        <v>3200.0</v>
       </c>
       <c r="D174" s="5" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E174" s="6"/>
       <c r="F174" s="7"/>
     </row>
     <row r="175">
       <c r="A175" s="8" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="B175" s="9" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="C175" s="9">
-        <v>395.0</v>
+        <v>5385.0</v>
       </c>
       <c r="D175" s="9" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E175" s="10"/>
       <c r="F175" s="11"/>
     </row>
     <row r="176">
       <c r="A176" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B176" s="5" t="s">
-        <v>203</v>
+        <v>47</v>
       </c>
       <c r="C176" s="5">
-        <v>4000.0</v>
+        <v>2750.0</v>
       </c>
       <c r="D176" s="5" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E176" s="6"/>
       <c r="F176" s="7"/>
     </row>
     <row r="177">
       <c r="A177" s="8" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="B177" s="9" t="s">
-        <v>104</v>
+        <v>196</v>
       </c>
       <c r="C177" s="9">
-        <v>10000.0</v>
+        <v>4600.0</v>
       </c>
       <c r="D177" s="9" t="s">
         <v>8</v>
@@ -4224,13 +4635,13 @@
     </row>
     <row r="178">
       <c r="A178" s="4" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B178" s="5" t="s">
-        <v>205</v>
+        <v>79</v>
       </c>
       <c r="C178" s="5">
-        <v>18500.0</v>
+        <v>3860.0</v>
       </c>
       <c r="D178" s="5" t="s">
         <v>8</v>
@@ -4240,13 +4651,13 @@
     </row>
     <row r="179">
       <c r="A179" s="8" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="B179" s="9" t="s">
-        <v>207</v>
+        <v>80</v>
       </c>
       <c r="C179" s="9">
-        <v>1020.0</v>
+        <v>7700.0</v>
       </c>
       <c r="D179" s="9" t="s">
         <v>8</v>
@@ -4256,13 +4667,13 @@
     </row>
     <row r="180">
       <c r="A180" s="4" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="B180" s="5" t="s">
-        <v>118</v>
+        <v>199</v>
       </c>
       <c r="C180" s="5">
-        <v>2350.0</v>
+        <v>8100.0</v>
       </c>
       <c r="D180" s="5" t="s">
         <v>8</v>
@@ -4272,13 +4683,13 @@
     </row>
     <row r="181">
       <c r="A181" s="8" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="B181" s="9" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C181" s="9">
-        <v>4690.0</v>
+        <v>3850.0</v>
       </c>
       <c r="D181" s="9" t="s">
         <v>8</v>
@@ -4288,13 +4699,13 @@
     </row>
     <row r="182">
       <c r="A182" s="4" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>135</v>
+        <v>203</v>
       </c>
       <c r="C182" s="5">
-        <v>700.0</v>
+        <v>290.0</v>
       </c>
       <c r="D182" s="5" t="s">
         <v>8</v>
@@ -4304,13 +4715,13 @@
     </row>
     <row r="183">
       <c r="A183" s="8" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="B183" s="9" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="C183" s="9">
-        <v>1230.0</v>
+        <v>790.0</v>
       </c>
       <c r="D183" s="9" t="s">
         <v>8</v>
@@ -4320,13 +4731,13 @@
     </row>
     <row r="184">
       <c r="A184" s="4" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="C184" s="5">
-        <v>1000.0</v>
+        <v>3600.0</v>
       </c>
       <c r="D184" s="5" t="s">
         <v>8</v>
@@ -4336,13 +4747,13 @@
     </row>
     <row r="185">
       <c r="A185" s="8" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="B185" s="9" t="s">
-        <v>84</v>
+        <v>207</v>
       </c>
       <c r="C185" s="9">
-        <v>1650.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D185" s="9" t="s">
         <v>8</v>
@@ -4352,13 +4763,13 @@
     </row>
     <row r="186">
       <c r="A186" s="4" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>68</v>
+        <v>203</v>
       </c>
       <c r="C186" s="5">
-        <v>6790.0</v>
+        <v>390.0</v>
       </c>
       <c r="D186" s="5" t="s">
         <v>8</v>
@@ -4368,13 +4779,13 @@
     </row>
     <row r="187">
       <c r="A187" s="8" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="B187" s="9" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
       <c r="C187" s="9">
-        <v>770.0</v>
+        <v>1805.0</v>
       </c>
       <c r="D187" s="9" t="s">
         <v>8</v>
@@ -4384,13 +4795,13 @@
     </row>
     <row r="188">
       <c r="A188" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="C188" s="5">
-        <v>1550.0</v>
+        <v>1200.0</v>
       </c>
       <c r="D188" s="5" t="s">
         <v>8</v>
@@ -4400,13 +4811,13 @@
     </row>
     <row r="189">
       <c r="A189" s="8" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="B189" s="9" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="C189" s="9">
-        <v>750.0</v>
+        <v>4360.0</v>
       </c>
       <c r="D189" s="9" t="s">
         <v>8</v>
@@ -4416,13 +4827,13 @@
     </row>
     <row r="190">
       <c r="A190" s="4" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="C190" s="5">
-        <v>565.0</v>
+        <v>3500.0</v>
       </c>
       <c r="D190" s="5" t="s">
         <v>8</v>
@@ -4432,109 +4843,109 @@
     </row>
     <row r="191">
       <c r="A191" s="8" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B191" s="9" t="s">
-        <v>184</v>
+        <v>214</v>
       </c>
       <c r="C191" s="9">
-        <v>100.0</v>
+        <v>310.0</v>
       </c>
       <c r="D191" s="9" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E191" s="10"/>
       <c r="F191" s="11"/>
     </row>
     <row r="192">
       <c r="A192" s="4" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="C192" s="5">
-        <v>590.0</v>
+        <v>500.0</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E192" s="6"/>
       <c r="F192" s="7"/>
     </row>
     <row r="193">
       <c r="A193" s="8" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="B193" s="9" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="C193" s="9">
-        <v>1180.0</v>
+        <v>795.0</v>
       </c>
       <c r="D193" s="9" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="E193" s="10"/>
       <c r="F193" s="11"/>
     </row>
     <row r="194">
       <c r="A194" s="4" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="B194" s="5" t="s">
-        <v>135</v>
+        <v>218</v>
       </c>
       <c r="C194" s="5">
-        <v>950.0</v>
+        <v>2000.0</v>
       </c>
       <c r="D194" s="5" t="s">
-        <v>8</v>
+        <v>219</v>
       </c>
       <c r="E194" s="6"/>
       <c r="F194" s="7"/>
     </row>
     <row r="195">
       <c r="A195" s="8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B195" s="9" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="C195" s="9">
-        <v>6500.0</v>
+        <v>395.0</v>
       </c>
       <c r="D195" s="9" t="s">
-        <v>8</v>
+        <v>219</v>
       </c>
       <c r="E195" s="10"/>
       <c r="F195" s="11"/>
     </row>
     <row r="196">
       <c r="A196" s="4" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="B196" s="5" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C196" s="5">
-        <v>1489.0</v>
+        <v>4000.0</v>
       </c>
       <c r="D196" s="5" t="s">
-        <v>8</v>
+        <v>219</v>
       </c>
       <c r="E196" s="6"/>
       <c r="F196" s="7"/>
     </row>
     <row r="197">
       <c r="A197" s="8" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B197" s="9" t="s">
-        <v>207</v>
+        <v>116</v>
       </c>
       <c r="C197" s="9">
-        <v>1169.0</v>
+        <v>10000.0</v>
       </c>
       <c r="D197" s="9" t="s">
         <v>8</v>
@@ -4544,13 +4955,13 @@
     </row>
     <row r="198">
       <c r="A198" s="4" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B198" s="5" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="C198" s="5">
-        <v>340.0</v>
+        <v>18500.0</v>
       </c>
       <c r="D198" s="5" t="s">
         <v>8</v>
@@ -4560,13 +4971,13 @@
     </row>
     <row r="199">
       <c r="A199" s="8" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B199" s="9" t="s">
-        <v>20</v>
+        <v>226</v>
       </c>
       <c r="C199" s="9">
-        <v>2710.0</v>
+        <v>1020.0</v>
       </c>
       <c r="D199" s="9" t="s">
         <v>8</v>
@@ -4576,29 +4987,29 @@
     </row>
     <row r="200">
       <c r="A200" s="4" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="B200" s="5" t="s">
-        <v>233</v>
+        <v>130</v>
       </c>
       <c r="C200" s="5">
-        <v>700.0</v>
+        <v>2350.0</v>
       </c>
       <c r="D200" s="5" t="s">
-        <v>200</v>
+        <v>8</v>
       </c>
       <c r="E200" s="6"/>
       <c r="F200" s="7"/>
     </row>
     <row r="201">
       <c r="A201" s="8" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B201" s="9" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C201" s="9">
-        <v>1300.0</v>
+        <v>4690.0</v>
       </c>
       <c r="D201" s="9" t="s">
         <v>8</v>
@@ -4608,13 +5019,13 @@
     </row>
     <row r="202">
       <c r="A202" s="4" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="B202" s="5" t="s">
-        <v>135</v>
+        <v>149</v>
       </c>
       <c r="C202" s="5">
-        <v>510.0</v>
+        <v>700.0</v>
       </c>
       <c r="D202" s="5" t="s">
         <v>8</v>
@@ -4624,13 +5035,13 @@
     </row>
     <row r="203">
       <c r="A203" s="8" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B203" s="9" t="s">
-        <v>237</v>
+        <v>207</v>
       </c>
       <c r="C203" s="9">
-        <v>659.0</v>
+        <v>1230.0</v>
       </c>
       <c r="D203" s="9" t="s">
         <v>8</v>
@@ -4640,13 +5051,13 @@
     </row>
     <row r="204">
       <c r="A204" s="4" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>67</v>
+        <v>233</v>
       </c>
       <c r="C204" s="5">
-        <v>899.0</v>
+        <v>1000.0</v>
       </c>
       <c r="D204" s="5" t="s">
         <v>8</v>
@@ -4656,13 +5067,13 @@
     </row>
     <row r="205">
       <c r="A205" s="8" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B205" s="9" t="s">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="C205" s="9">
-        <v>1710.0</v>
+        <v>1650.0</v>
       </c>
       <c r="D205" s="9" t="s">
         <v>8</v>
@@ -4672,13 +5083,13 @@
     </row>
     <row r="206">
       <c r="A206" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>184</v>
+        <v>80</v>
       </c>
       <c r="C206" s="5">
-        <v>1690.0</v>
+        <v>6790.0</v>
       </c>
       <c r="D206" s="5" t="s">
         <v>8</v>
@@ -4688,13 +5099,13 @@
     </row>
     <row r="207">
       <c r="A207" s="8" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="B207" s="9" t="s">
-        <v>38</v>
+        <v>236</v>
       </c>
       <c r="C207" s="9">
-        <v>1070.0</v>
+        <v>770.0</v>
       </c>
       <c r="D207" s="9" t="s">
         <v>8</v>
@@ -4704,13 +5115,13 @@
     </row>
     <row r="208">
       <c r="A208" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C208" s="5">
-        <v>1410.0</v>
+        <v>1550.0</v>
       </c>
       <c r="D208" s="5" t="s">
         <v>8</v>
@@ -4720,13 +5131,13 @@
     </row>
     <row r="209">
       <c r="A209" s="8" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B209" s="9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C209" s="9">
-        <v>25600.0</v>
+        <v>750.0</v>
       </c>
       <c r="D209" s="9" t="s">
         <v>8</v>
@@ -4736,61 +5147,61 @@
     </row>
     <row r="210">
       <c r="A210" s="4" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>84</v>
+        <v>226</v>
       </c>
       <c r="C210" s="5">
-        <v>1070.0</v>
+        <v>565.0</v>
       </c>
       <c r="D210" s="5" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="E210" s="6"/>
       <c r="F210" s="7"/>
     </row>
     <row r="211">
       <c r="A211" s="8" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B211" s="9" t="s">
-        <v>67</v>
+        <v>203</v>
       </c>
       <c r="C211" s="9">
-        <v>2120.0</v>
+        <v>100.0</v>
       </c>
       <c r="D211" s="9" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="E211" s="10"/>
       <c r="F211" s="11"/>
     </row>
     <row r="212">
       <c r="A212" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>38</v>
+        <v>243</v>
       </c>
       <c r="C212" s="5">
-        <v>4210.0</v>
+        <v>590.0</v>
       </c>
       <c r="D212" s="5" t="s">
-        <v>245</v>
+        <v>8</v>
       </c>
       <c r="E212" s="6"/>
       <c r="F212" s="7"/>
     </row>
     <row r="213">
       <c r="A213" s="8" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="B213" s="9" t="s">
-        <v>247</v>
+        <v>159</v>
       </c>
       <c r="C213" s="9">
-        <v>300.0</v>
+        <v>1180.0</v>
       </c>
       <c r="D213" s="9" t="s">
         <v>8</v>
@@ -4799,583 +5210,1161 @@
       <c r="F213" s="11"/>
     </row>
     <row r="214">
-      <c r="A214" s="4"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="5"/>
-      <c r="D214" s="5"/>
+      <c r="A214" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C214" s="5">
+        <v>950.0</v>
+      </c>
+      <c r="D214" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E214" s="6"/>
       <c r="F214" s="7"/>
     </row>
     <row r="215">
-      <c r="A215" s="8"/>
-      <c r="B215" s="9"/>
-      <c r="C215" s="9"/>
-      <c r="D215" s="9"/>
+      <c r="A215" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B215" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C215" s="9">
+        <v>6500.0</v>
+      </c>
+      <c r="D215" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E215" s="10"/>
       <c r="F215" s="11"/>
     </row>
     <row r="216">
-      <c r="A216" s="4"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="5"/>
-      <c r="D216" s="5"/>
+      <c r="A216" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="C216" s="5">
+        <v>1489.0</v>
+      </c>
+      <c r="D216" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E216" s="6"/>
       <c r="F216" s="7"/>
     </row>
     <row r="217">
-      <c r="A217" s="8"/>
-      <c r="B217" s="9"/>
-      <c r="C217" s="9"/>
-      <c r="D217" s="9"/>
+      <c r="A217" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B217" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C217" s="9">
+        <v>1169.0</v>
+      </c>
+      <c r="D217" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E217" s="10"/>
       <c r="F217" s="11"/>
     </row>
     <row r="218">
-      <c r="A218" s="4"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="5"/>
-      <c r="D218" s="5"/>
+      <c r="A218" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C218" s="5">
+        <v>700.0</v>
+      </c>
+      <c r="D218" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E218" s="6"/>
       <c r="F218" s="7"/>
     </row>
     <row r="219">
-      <c r="A219" s="8"/>
-      <c r="B219" s="9"/>
-      <c r="C219" s="9"/>
-      <c r="D219" s="9"/>
+      <c r="A219" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B219" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C219" s="9">
+        <v>2710.0</v>
+      </c>
+      <c r="D219" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E219" s="10"/>
       <c r="F219" s="11"/>
     </row>
     <row r="220">
-      <c r="A220" s="4"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
-      <c r="E220" s="6"/>
+      <c r="A220" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="B220" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C220" s="40">
+        <v>3000.0</v>
+      </c>
+      <c r="D220" s="17" t="s">
+        <v>8</v>
+      </c>
+      <c r="E220" s="36"/>
       <c r="F220" s="7"/>
     </row>
     <row r="221">
-      <c r="A221" s="8"/>
-      <c r="B221" s="9"/>
-      <c r="C221" s="9"/>
-      <c r="D221" s="9"/>
-      <c r="E221" s="10"/>
+      <c r="A221" s="32" t="s">
+        <v>251</v>
+      </c>
+      <c r="B221" s="29" t="s">
+        <v>250</v>
+      </c>
+      <c r="C221" s="47">
+        <v>900.0</v>
+      </c>
+      <c r="D221" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="E221" s="36"/>
       <c r="F221" s="11"/>
     </row>
     <row r="222">
-      <c r="A222" s="4"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="5"/>
+      <c r="A222" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C222" s="5">
+        <v>700.0</v>
+      </c>
+      <c r="D222" s="5" t="s">
+        <v>219</v>
+      </c>
       <c r="E222" s="6"/>
       <c r="F222" s="7"/>
     </row>
     <row r="223">
-      <c r="A223" s="8"/>
-      <c r="B223" s="9"/>
-      <c r="C223" s="9"/>
-      <c r="D223" s="9"/>
+      <c r="A223" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="B223" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C223" s="9">
+        <v>1300.0</v>
+      </c>
+      <c r="D223" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E223" s="10"/>
       <c r="F223" s="11"/>
     </row>
     <row r="224">
-      <c r="A224" s="4"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
+      <c r="A224" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C224" s="5">
+        <v>510.0</v>
+      </c>
+      <c r="D224" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E224" s="6"/>
       <c r="F224" s="7"/>
     </row>
     <row r="225">
-      <c r="A225" s="8"/>
-      <c r="B225" s="9"/>
-      <c r="C225" s="9"/>
-      <c r="D225" s="9"/>
+      <c r="A225" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B225" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C225" s="9">
+        <v>659.0</v>
+      </c>
+      <c r="D225" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E225" s="10"/>
       <c r="F225" s="11"/>
     </row>
     <row r="226">
-      <c r="A226" s="4"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="5"/>
-      <c r="D226" s="5"/>
+      <c r="A226" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C226" s="5">
+        <v>899.0</v>
+      </c>
+      <c r="D226" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E226" s="6"/>
       <c r="F226" s="7"/>
     </row>
     <row r="227">
-      <c r="A227" s="8"/>
-      <c r="B227" s="9"/>
-      <c r="C227" s="9"/>
-      <c r="D227" s="9"/>
+      <c r="A227" s="8" t="s">
+        <v>258</v>
+      </c>
+      <c r="B227" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="C227" s="9">
+        <v>1710.0</v>
+      </c>
+      <c r="D227" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E227" s="10"/>
       <c r="F227" s="11"/>
     </row>
     <row r="228">
-      <c r="A228" s="4"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="5"/>
-      <c r="D228" s="5"/>
+      <c r="A228" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C228" s="5">
+        <v>1690.0</v>
+      </c>
+      <c r="D228" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E228" s="6"/>
       <c r="F228" s="7"/>
     </row>
     <row r="229">
-      <c r="A229" s="8"/>
-      <c r="B229" s="9"/>
-      <c r="C229" s="9"/>
-      <c r="D229" s="9"/>
+      <c r="A229" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B229" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C229" s="9">
+        <v>1070.0</v>
+      </c>
+      <c r="D229" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E229" s="10"/>
       <c r="F229" s="11"/>
     </row>
     <row r="230">
-      <c r="A230" s="4"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="5"/>
-      <c r="D230" s="5"/>
+      <c r="A230" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="C230" s="5">
+        <v>1410.0</v>
+      </c>
+      <c r="D230" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E230" s="6"/>
       <c r="F230" s="7"/>
     </row>
     <row r="231">
-      <c r="A231" s="8"/>
-      <c r="B231" s="9"/>
-      <c r="C231" s="9"/>
-      <c r="D231" s="9"/>
+      <c r="A231" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B231" s="9" t="s">
+        <v>263</v>
+      </c>
+      <c r="C231" s="9">
+        <v>25600.0</v>
+      </c>
+      <c r="D231" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E231" s="10"/>
       <c r="F231" s="11"/>
     </row>
     <row r="232">
-      <c r="A232" s="4"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="5"/>
-      <c r="D232" s="5"/>
+      <c r="A232" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C232" s="5">
+        <v>1070.0</v>
+      </c>
+      <c r="D232" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="E232" s="6"/>
       <c r="F232" s="7"/>
     </row>
     <row r="233">
-      <c r="A233" s="8"/>
-      <c r="B233" s="9"/>
-      <c r="C233" s="9"/>
-      <c r="D233" s="9"/>
+      <c r="A233" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="B233" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C233" s="9">
+        <v>2120.0</v>
+      </c>
+      <c r="D233" s="9" t="s">
+        <v>265</v>
+      </c>
       <c r="E233" s="10"/>
       <c r="F233" s="11"/>
     </row>
     <row r="234">
-      <c r="A234" s="4"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="5"/>
-      <c r="D234" s="5"/>
+      <c r="A234" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C234" s="5">
+        <v>4210.0</v>
+      </c>
+      <c r="D234" s="5" t="s">
+        <v>265</v>
+      </c>
       <c r="E234" s="6"/>
       <c r="F234" s="7"/>
     </row>
     <row r="235">
-      <c r="A235" s="8"/>
-      <c r="B235" s="9"/>
-      <c r="C235" s="9"/>
-      <c r="D235" s="9"/>
+      <c r="A235" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B235" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="C235" s="9">
+        <v>300.0</v>
+      </c>
+      <c r="D235" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E235" s="10"/>
       <c r="F235" s="11"/>
     </row>
     <row r="236">
-      <c r="A236" s="4"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="5"/>
-      <c r="D236" s="5"/>
+      <c r="A236" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>269</v>
+      </c>
+      <c r="C236" s="5">
+        <v>400.0</v>
+      </c>
+      <c r="D236" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E236" s="6"/>
       <c r="F236" s="7"/>
     </row>
     <row r="237">
-      <c r="A237" s="8"/>
-      <c r="B237" s="9"/>
-      <c r="C237" s="9"/>
-      <c r="D237" s="9"/>
+      <c r="A237" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B237" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="C237" s="9">
+        <v>1100.0</v>
+      </c>
+      <c r="D237" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E237" s="10"/>
       <c r="F237" s="11"/>
     </row>
     <row r="238">
-      <c r="A238" s="4"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="5"/>
-      <c r="D238" s="5"/>
+      <c r="A238" s="31" t="s">
+        <v>268</v>
+      </c>
+      <c r="B238" s="18" t="s">
+        <v>271</v>
+      </c>
+      <c r="C238" s="40">
+        <v>2050.0</v>
+      </c>
+      <c r="D238" s="17" t="s">
+        <v>8</v>
+      </c>
       <c r="E238" s="6"/>
       <c r="F238" s="7"/>
     </row>
     <row r="239">
-      <c r="A239" s="8"/>
-      <c r="B239" s="9"/>
-      <c r="C239" s="9"/>
-      <c r="D239" s="9"/>
+      <c r="A239" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B239" s="9" t="s">
+        <v>273</v>
+      </c>
+      <c r="C239" s="9">
+        <v>2910.0</v>
+      </c>
+      <c r="D239" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E239" s="10"/>
       <c r="F239" s="11"/>
     </row>
     <row r="240">
-      <c r="A240" s="4"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="5"/>
-      <c r="D240" s="5"/>
+      <c r="A240" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>274</v>
+      </c>
+      <c r="C240" s="5">
+        <v>3750.0</v>
+      </c>
+      <c r="D240" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E240" s="6"/>
       <c r="F240" s="7"/>
     </row>
     <row r="241">
-      <c r="A241" s="8"/>
-      <c r="B241" s="9"/>
-      <c r="C241" s="9"/>
-      <c r="D241" s="9"/>
+      <c r="A241" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B241" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="C241" s="9">
+        <v>135.0</v>
+      </c>
+      <c r="D241" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E241" s="10"/>
       <c r="F241" s="11"/>
     </row>
     <row r="242">
-      <c r="A242" s="4"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="5"/>
-      <c r="D242" s="5"/>
+      <c r="A242" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="C242" s="5">
+        <v>3500.0</v>
+      </c>
+      <c r="D242" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E242" s="6"/>
       <c r="F242" s="7"/>
     </row>
     <row r="243">
-      <c r="A243" s="8"/>
-      <c r="B243" s="9"/>
-      <c r="C243" s="9"/>
-      <c r="D243" s="9"/>
+      <c r="A243" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B243" s="9" t="s">
+        <v>278</v>
+      </c>
+      <c r="C243" s="9">
+        <v>6980.0</v>
+      </c>
+      <c r="D243" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E243" s="10"/>
       <c r="F243" s="11"/>
     </row>
     <row r="244">
-      <c r="A244" s="4"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="5"/>
-      <c r="D244" s="5"/>
+      <c r="A244" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="C244" s="5">
+        <v>1930.0</v>
+      </c>
+      <c r="D244" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E244" s="6"/>
       <c r="F244" s="7"/>
     </row>
     <row r="245">
-      <c r="A245" s="8"/>
-      <c r="B245" s="9"/>
-      <c r="C245" s="9"/>
-      <c r="D245" s="9"/>
+      <c r="A245" s="8" t="s">
+        <v>279</v>
+      </c>
+      <c r="B245" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C245" s="9">
+        <v>1355.0</v>
+      </c>
+      <c r="D245" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E245" s="10"/>
       <c r="F245" s="11"/>
     </row>
     <row r="246">
-      <c r="A246" s="4"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="5"/>
-      <c r="D246" s="5"/>
+      <c r="A246" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="C246" s="5">
+        <v>750.0</v>
+      </c>
+      <c r="D246" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E246" s="6"/>
       <c r="F246" s="7"/>
     </row>
     <row r="247">
-      <c r="A247" s="8"/>
-      <c r="B247" s="9"/>
-      <c r="C247" s="9"/>
-      <c r="D247" s="9"/>
+      <c r="A247" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B247" s="9" t="s">
+        <v>284</v>
+      </c>
+      <c r="C247" s="9">
+        <v>7450.0</v>
+      </c>
+      <c r="D247" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E247" s="10"/>
       <c r="F247" s="11"/>
     </row>
     <row r="248">
-      <c r="A248" s="4"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="5"/>
-      <c r="D248" s="5"/>
+      <c r="A248" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="B248" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="C248" s="5">
+        <v>810.0</v>
+      </c>
+      <c r="D248" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E248" s="6"/>
       <c r="F248" s="7"/>
     </row>
     <row r="249">
-      <c r="A249" s="8"/>
-      <c r="B249" s="9"/>
-      <c r="C249" s="9"/>
-      <c r="D249" s="9"/>
+      <c r="A249" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B249" s="9">
+        <v>1.0</v>
+      </c>
+      <c r="C249" s="9">
+        <v>230.0</v>
+      </c>
+      <c r="D249" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E249" s="10"/>
       <c r="F249" s="11"/>
     </row>
     <row r="250">
-      <c r="A250" s="4"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="5"/>
-      <c r="D250" s="5"/>
+      <c r="A250" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="C250" s="5">
+        <v>350.0</v>
+      </c>
+      <c r="D250" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E250" s="6"/>
       <c r="F250" s="7"/>
     </row>
     <row r="251">
-      <c r="A251" s="8"/>
-      <c r="B251" s="9"/>
-      <c r="C251" s="9"/>
-      <c r="D251" s="9"/>
+      <c r="A251" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>289</v>
+      </c>
+      <c r="C251" s="9">
+        <v>1320.0</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E251" s="10"/>
       <c r="F251" s="11"/>
     </row>
     <row r="252">
-      <c r="A252" s="4"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="5"/>
-      <c r="D252" s="5"/>
+      <c r="A252" s="4" t="s">
+        <v>287</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="C252" s="5">
+        <v>7010.0</v>
+      </c>
+      <c r="D252" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E252" s="6"/>
       <c r="F252" s="7"/>
     </row>
     <row r="253">
-      <c r="A253" s="8"/>
-      <c r="B253" s="9"/>
-      <c r="C253" s="9"/>
-      <c r="D253" s="9"/>
+      <c r="A253" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="B253" s="9" t="s">
+        <v>291</v>
+      </c>
+      <c r="C253" s="9">
+        <v>3520.0</v>
+      </c>
+      <c r="D253" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E253" s="10"/>
       <c r="F253" s="11"/>
     </row>
     <row r="254">
-      <c r="A254" s="4"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="5"/>
-      <c r="D254" s="5"/>
+      <c r="A254" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="C254" s="5">
+        <v>350.0</v>
+      </c>
+      <c r="D254" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E254" s="6"/>
       <c r="F254" s="7"/>
     </row>
     <row r="255">
-      <c r="A255" s="8"/>
-      <c r="B255" s="9"/>
-      <c r="C255" s="9"/>
-      <c r="D255" s="9"/>
+      <c r="A255" s="8" t="s">
+        <v>293</v>
+      </c>
+      <c r="B255" s="9" t="s">
+        <v>294</v>
+      </c>
+      <c r="C255" s="9">
+        <v>410.0</v>
+      </c>
+      <c r="D255" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E255" s="10"/>
       <c r="F255" s="11"/>
     </row>
     <row r="256">
-      <c r="A256" s="4"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="5"/>
-      <c r="D256" s="5"/>
+      <c r="A256" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>294</v>
+      </c>
+      <c r="C256" s="5">
+        <v>510.0</v>
+      </c>
+      <c r="D256" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E256" s="6"/>
       <c r="F256" s="7"/>
     </row>
     <row r="257">
-      <c r="A257" s="8"/>
-      <c r="B257" s="9"/>
-      <c r="C257" s="9"/>
-      <c r="D257" s="9"/>
+      <c r="A257" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="B257" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="C257" s="9">
+        <v>430.0</v>
+      </c>
+      <c r="D257" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E257" s="10"/>
       <c r="F257" s="11"/>
     </row>
     <row r="258">
-      <c r="A258" s="4"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="5"/>
-      <c r="D258" s="5"/>
+      <c r="A258" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C258" s="5">
+        <v>560.0</v>
+      </c>
+      <c r="D258" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E258" s="6"/>
       <c r="F258" s="7"/>
     </row>
     <row r="259">
-      <c r="A259" s="8"/>
-      <c r="B259" s="9"/>
-      <c r="C259" s="9"/>
-      <c r="D259" s="9"/>
+      <c r="A259" s="8" t="s">
+        <v>298</v>
+      </c>
+      <c r="B259" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C259" s="9">
+        <v>1699.0</v>
+      </c>
+      <c r="D259" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E259" s="10"/>
       <c r="F259" s="11"/>
     </row>
     <row r="260">
-      <c r="A260" s="4"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="5"/>
-      <c r="D260" s="5"/>
+      <c r="A260" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="C260" s="5">
+        <v>2150.0</v>
+      </c>
+      <c r="D260" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E260" s="6"/>
       <c r="F260" s="7"/>
     </row>
     <row r="261">
-      <c r="A261" s="8"/>
-      <c r="B261" s="9"/>
-      <c r="C261" s="9"/>
-      <c r="D261" s="9"/>
+      <c r="A261" s="8" t="s">
+        <v>301</v>
+      </c>
+      <c r="B261" s="9" t="s">
+        <v>302</v>
+      </c>
+      <c r="C261" s="9">
+        <v>1000.0</v>
+      </c>
+      <c r="D261" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E261" s="10"/>
       <c r="F261" s="11"/>
     </row>
     <row r="262">
-      <c r="A262" s="4"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="5"/>
-      <c r="D262" s="5"/>
+      <c r="A262" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="B262" s="5">
+        <v>1.0</v>
+      </c>
+      <c r="C262" s="5">
+        <v>1200.0</v>
+      </c>
+      <c r="D262" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E262" s="6"/>
       <c r="F262" s="7"/>
     </row>
     <row r="263">
-      <c r="A263" s="8"/>
-      <c r="B263" s="9"/>
-      <c r="C263" s="9"/>
-      <c r="D263" s="9"/>
+      <c r="A263" s="8" t="s">
+        <v>303</v>
+      </c>
+      <c r="B263" s="9" t="s">
+        <v>304</v>
+      </c>
+      <c r="C263" s="9">
+        <v>3510.0</v>
+      </c>
+      <c r="D263" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E263" s="10"/>
       <c r="F263" s="11"/>
     </row>
     <row r="264">
-      <c r="A264" s="4"/>
-      <c r="B264" s="5"/>
-      <c r="C264" s="5"/>
-      <c r="D264" s="5"/>
+      <c r="A264" s="4" t="s">
+        <v>305</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="C264" s="5">
+        <v>680.0</v>
+      </c>
+      <c r="D264" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E264" s="6"/>
       <c r="F264" s="7"/>
     </row>
     <row r="265">
-      <c r="A265" s="8"/>
-      <c r="B265" s="9"/>
-      <c r="C265" s="9"/>
-      <c r="D265" s="9"/>
+      <c r="A265" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="B265" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="C265" s="9">
+        <v>2700.0</v>
+      </c>
+      <c r="D265" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E265" s="10"/>
       <c r="F265" s="11"/>
     </row>
     <row r="266">
-      <c r="A266" s="4"/>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5"/>
-      <c r="D266" s="5"/>
+      <c r="A266" s="4" t="s">
+        <v>307</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C266" s="5">
+        <v>1110.0</v>
+      </c>
+      <c r="D266" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E266" s="6"/>
       <c r="F266" s="7"/>
     </row>
     <row r="267">
-      <c r="A267" s="8"/>
-      <c r="B267" s="9"/>
-      <c r="C267" s="9"/>
-      <c r="D267" s="9"/>
+      <c r="A267" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B267" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C267" s="9">
+        <v>2215.0</v>
+      </c>
+      <c r="D267" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E267" s="10"/>
       <c r="F267" s="11"/>
     </row>
     <row r="268">
-      <c r="A268" s="4"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="5"/>
-      <c r="D268" s="5"/>
+      <c r="A268" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C268" s="5">
+        <v>5550.0</v>
+      </c>
+      <c r="D268" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E268" s="6"/>
       <c r="F268" s="7"/>
     </row>
     <row r="269">
-      <c r="A269" s="8"/>
-      <c r="B269" s="9"/>
-      <c r="C269" s="9"/>
-      <c r="D269" s="9"/>
+      <c r="A269" s="8" t="s">
+        <v>309</v>
+      </c>
+      <c r="B269" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C269" s="9">
+        <v>11100.0</v>
+      </c>
+      <c r="D269" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E269" s="10"/>
       <c r="F269" s="11"/>
     </row>
     <row r="270">
-      <c r="A270" s="4"/>
-      <c r="B270" s="5"/>
-      <c r="C270" s="5"/>
-      <c r="D270" s="5"/>
+      <c r="A270" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>311</v>
+      </c>
+      <c r="C270" s="5">
+        <v>2800.0</v>
+      </c>
+      <c r="D270" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E270" s="6"/>
       <c r="F270" s="7"/>
     </row>
     <row r="271">
-      <c r="A271" s="8"/>
-      <c r="B271" s="9"/>
-      <c r="C271" s="9"/>
-      <c r="D271" s="9"/>
+      <c r="A271" s="8" t="s">
+        <v>310</v>
+      </c>
+      <c r="B271" s="9" t="s">
+        <v>312</v>
+      </c>
+      <c r="C271" s="9">
+        <v>5600.0</v>
+      </c>
+      <c r="D271" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E271" s="10"/>
       <c r="F271" s="11"/>
     </row>
     <row r="272">
-      <c r="A272" s="4"/>
-      <c r="B272" s="5"/>
-      <c r="C272" s="5"/>
-      <c r="D272" s="5"/>
+      <c r="A272" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>314</v>
+      </c>
+      <c r="C272" s="5">
+        <v>2500.0</v>
+      </c>
+      <c r="D272" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E272" s="6"/>
       <c r="F272" s="7"/>
     </row>
     <row r="273">
-      <c r="A273" s="8"/>
-      <c r="B273" s="9"/>
-      <c r="C273" s="9"/>
-      <c r="D273" s="9"/>
+      <c r="A273" s="8" t="s">
+        <v>313</v>
+      </c>
+      <c r="B273" s="9" t="s">
+        <v>315</v>
+      </c>
+      <c r="C273" s="9">
+        <v>4850.0</v>
+      </c>
+      <c r="D273" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E273" s="10"/>
       <c r="F273" s="11"/>
     </row>
     <row r="274">
-      <c r="A274" s="4"/>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5"/>
-      <c r="D274" s="5"/>
+      <c r="A274" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="C274" s="5">
+        <v>4690.0</v>
+      </c>
+      <c r="D274" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E274" s="6"/>
       <c r="F274" s="7"/>
     </row>
     <row r="275">
-      <c r="A275" s="8"/>
-      <c r="B275" s="9"/>
-      <c r="C275" s="9"/>
-      <c r="D275" s="9"/>
+      <c r="A275" s="8" t="s">
+        <v>316</v>
+      </c>
+      <c r="B275" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="C275" s="9">
+        <v>9375.0</v>
+      </c>
+      <c r="D275" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E275" s="10"/>
       <c r="F275" s="11"/>
     </row>
     <row r="276">
-      <c r="A276" s="4"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="5"/>
-      <c r="D276" s="5"/>
+      <c r="A276" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C276" s="5">
+        <v>289.0</v>
+      </c>
+      <c r="D276" s="5" t="s">
+        <v>320</v>
+      </c>
       <c r="E276" s="6"/>
       <c r="F276" s="7"/>
     </row>
     <row r="277">
-      <c r="A277" s="8"/>
-      <c r="B277" s="9"/>
-      <c r="C277" s="9"/>
-      <c r="D277" s="9"/>
+      <c r="A277" s="13" t="s">
+        <v>321</v>
+      </c>
+      <c r="B277" s="15" t="s">
+        <v>322</v>
+      </c>
+      <c r="C277" s="21">
+        <v>379.0</v>
+      </c>
+      <c r="D277" s="14" t="s">
+        <v>320</v>
+      </c>
       <c r="E277" s="10"/>
       <c r="F277" s="11"/>
     </row>
     <row r="278">
-      <c r="A278" s="4"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="5"/>
-      <c r="D278" s="5"/>
+      <c r="A278" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="C278" s="5">
+        <v>710.0</v>
+      </c>
+      <c r="D278" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E278" s="6"/>
       <c r="F278" s="7"/>
     </row>
     <row r="279">
-      <c r="A279" s="8"/>
-      <c r="B279" s="9"/>
-      <c r="C279" s="9"/>
-      <c r="D279" s="9"/>
+      <c r="A279" s="8" t="s">
+        <v>323</v>
+      </c>
+      <c r="B279" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C279" s="39">
+        <v>1415.0</v>
+      </c>
+      <c r="D279" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E279" s="10"/>
       <c r="F279" s="11"/>
     </row>
     <row r="280">
-      <c r="A280" s="4"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="5"/>
-      <c r="D280" s="5"/>
+      <c r="A280" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C280" s="5">
+        <v>2000.0</v>
+      </c>
+      <c r="D280" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E280" s="6"/>
       <c r="F280" s="7"/>
     </row>
     <row r="281">
-      <c r="A281" s="8"/>
-      <c r="B281" s="9"/>
-      <c r="C281" s="9"/>
-      <c r="D281" s="9"/>
+      <c r="A281" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B281" s="9" t="s">
+        <v>326</v>
+      </c>
+      <c r="C281" s="9">
+        <v>8000.0</v>
+      </c>
+      <c r="D281" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E281" s="10"/>
       <c r="F281" s="11"/>
     </row>
     <row r="282">
-      <c r="A282" s="4"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="5"/>
-      <c r="D282" s="5"/>
+      <c r="A282" s="4" t="s">
+        <v>324</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="C282" s="5">
+        <v>4000.0</v>
+      </c>
+      <c r="D282" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E282" s="6"/>
       <c r="F282" s="7"/>
     </row>
     <row r="283">
-      <c r="A283" s="8"/>
-      <c r="B283" s="9"/>
-      <c r="C283" s="9"/>
-      <c r="D283" s="9"/>
+      <c r="A283" s="8" t="s">
+        <v>324</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="C283" s="39">
+        <v>20000.0</v>
+      </c>
+      <c r="D283" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E283" s="10"/>
       <c r="F283" s="11"/>
     </row>
     <row r="284">
-      <c r="A284" s="4"/>
-      <c r="B284" s="5"/>
-      <c r="C284" s="5"/>
-      <c r="D284" s="5"/>
+      <c r="A284" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C284" s="5">
+        <v>1800.0</v>
+      </c>
+      <c r="D284" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E284" s="6"/>
       <c r="F284" s="7"/>
     </row>
     <row r="285">
-      <c r="A285" s="8"/>
-      <c r="B285" s="9"/>
-      <c r="C285" s="9"/>
-      <c r="D285" s="9"/>
+      <c r="A285" s="8" t="s">
+        <v>329</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C285" s="9">
+        <v>3700.0</v>
+      </c>
+      <c r="D285" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E285" s="10"/>
       <c r="F285" s="11"/>
     </row>
     <row r="286">
-      <c r="A286" s="4"/>
+      <c r="A286" s="4" t="s">
+        <v>330</v>
+      </c>
       <c r="B286" s="5"/>
       <c r="C286" s="5"/>
       <c r="D286" s="5"/>
@@ -5383,330 +6372,656 @@
       <c r="F286" s="7"/>
     </row>
     <row r="287">
-      <c r="A287" s="8"/>
-      <c r="B287" s="9"/>
-      <c r="C287" s="9"/>
-      <c r="D287" s="9"/>
+      <c r="A287" s="8" t="s">
+        <v>331</v>
+      </c>
+      <c r="B287" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="C287" s="9">
+        <v>2180.0</v>
+      </c>
+      <c r="D287" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E287" s="10"/>
       <c r="F287" s="11"/>
     </row>
     <row r="288">
-      <c r="A288" s="4"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="5"/>
-      <c r="D288" s="5"/>
+      <c r="A288" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C288" s="5">
+        <v>305.0</v>
+      </c>
+      <c r="D288" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E288" s="6"/>
       <c r="F288" s="7"/>
     </row>
     <row r="289">
-      <c r="A289" s="8"/>
-      <c r="B289" s="9"/>
-      <c r="C289" s="9"/>
-      <c r="D289" s="9"/>
+      <c r="A289" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B289" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C289" s="9">
+        <v>515.0</v>
+      </c>
+      <c r="D289" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E289" s="10"/>
       <c r="F289" s="11"/>
     </row>
     <row r="290">
-      <c r="A290" s="4"/>
-      <c r="B290" s="5"/>
-      <c r="C290" s="5"/>
-      <c r="D290" s="5"/>
+      <c r="A290" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C290" s="5">
+        <v>12130.0</v>
+      </c>
+      <c r="D290" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E290" s="6"/>
       <c r="F290" s="7"/>
     </row>
     <row r="291">
-      <c r="A291" s="8"/>
-      <c r="B291" s="9"/>
-      <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
+      <c r="A291" s="8" t="s">
+        <v>332</v>
+      </c>
+      <c r="B291" s="9" t="s">
+        <v>336</v>
+      </c>
+      <c r="C291" s="9">
+        <v>21000.0</v>
+      </c>
+      <c r="D291" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E291" s="10"/>
       <c r="F291" s="11"/>
     </row>
     <row r="292">
-      <c r="A292" s="4"/>
-      <c r="B292" s="5"/>
-      <c r="C292" s="5"/>
-      <c r="D292" s="5"/>
+      <c r="A292" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="C292" s="5">
+        <v>305.0</v>
+      </c>
+      <c r="D292" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E292" s="6"/>
       <c r="F292" s="7"/>
     </row>
     <row r="293">
-      <c r="A293" s="8"/>
-      <c r="B293" s="9"/>
-      <c r="C293" s="9"/>
-      <c r="D293" s="9"/>
+      <c r="A293" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B293" s="9" t="s">
+        <v>338</v>
+      </c>
+      <c r="C293" s="9">
+        <v>360.0</v>
+      </c>
+      <c r="D293" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E293" s="10"/>
       <c r="F293" s="11"/>
     </row>
     <row r="294">
-      <c r="A294" s="4"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="5"/>
-      <c r="D294" s="5"/>
+      <c r="A294" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C294" s="5">
+        <v>12130.0</v>
+      </c>
+      <c r="D294" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E294" s="6"/>
       <c r="F294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="8"/>
-      <c r="B295" s="9"/>
-      <c r="C295" s="9"/>
-      <c r="D295" s="9"/>
+      <c r="A295" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="B295" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="C295" s="9">
+        <v>14340.0</v>
+      </c>
+      <c r="D295" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E295" s="10"/>
       <c r="F295" s="11"/>
     </row>
     <row r="296">
-      <c r="A296" s="4"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="5"/>
+      <c r="A296" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C296" s="5">
+        <v>1150.0</v>
+      </c>
       <c r="D296" s="5"/>
       <c r="E296" s="6"/>
       <c r="F296" s="7"/>
     </row>
     <row r="297">
-      <c r="A297" s="8"/>
-      <c r="B297" s="9"/>
-      <c r="C297" s="9"/>
-      <c r="D297" s="9"/>
+      <c r="A297" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B297" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="C297" s="9">
+        <v>305.0</v>
+      </c>
+      <c r="D297" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E297" s="10"/>
       <c r="F297" s="11"/>
     </row>
     <row r="298">
-      <c r="A298" s="4"/>
-      <c r="B298" s="5"/>
-      <c r="C298" s="5"/>
-      <c r="D298" s="5"/>
+      <c r="A298" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="C298" s="5">
+        <v>960.0</v>
+      </c>
+      <c r="D298" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E298" s="6"/>
       <c r="F298" s="7"/>
     </row>
     <row r="299">
-      <c r="A299" s="8"/>
-      <c r="B299" s="9"/>
-      <c r="C299" s="9"/>
-      <c r="D299" s="9"/>
+      <c r="A299" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="B299" s="9" t="s">
+        <v>335</v>
+      </c>
+      <c r="C299" s="9">
+        <v>12130.0</v>
+      </c>
+      <c r="D299" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E299" s="10"/>
       <c r="F299" s="11"/>
     </row>
     <row r="300">
-      <c r="A300" s="4"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="5"/>
-      <c r="D300" s="5"/>
+      <c r="A300" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="C300" s="5">
+        <v>15410.0</v>
+      </c>
+      <c r="D300" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E300" s="6"/>
       <c r="F300" s="7"/>
     </row>
     <row r="301">
-      <c r="A301" s="8"/>
-      <c r="B301" s="9"/>
-      <c r="C301" s="9"/>
-      <c r="D301" s="9"/>
+      <c r="A301" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B301" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="C301" s="9">
+        <v>240.0</v>
+      </c>
+      <c r="D301" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E301" s="10"/>
       <c r="F301" s="11"/>
     </row>
     <row r="302">
-      <c r="A302" s="4"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="5"/>
-      <c r="D302" s="5"/>
+      <c r="A302" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="C302" s="5">
+        <v>5295.0</v>
+      </c>
+      <c r="D302" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E302" s="6"/>
       <c r="F302" s="7"/>
     </row>
     <row r="303">
-      <c r="A303" s="8"/>
-      <c r="B303" s="9"/>
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
+      <c r="A303" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B303" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="C303" s="9">
+        <v>10590.0</v>
+      </c>
+      <c r="D303" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E303" s="10"/>
       <c r="F303" s="11"/>
     </row>
     <row r="304">
-      <c r="A304" s="4"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="5"/>
-      <c r="D304" s="5"/>
+      <c r="A304" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>297</v>
+      </c>
+      <c r="C304" s="5">
+        <v>211.0</v>
+      </c>
+      <c r="D304" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E304" s="6"/>
       <c r="F304" s="7"/>
     </row>
     <row r="305">
-      <c r="A305" s="8"/>
-      <c r="B305" s="9"/>
-      <c r="C305" s="9"/>
-      <c r="D305" s="9"/>
+      <c r="A305" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B305" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="C305" s="39">
+        <v>10150.0</v>
+      </c>
+      <c r="D305" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E305" s="10"/>
       <c r="F305" s="11"/>
     </row>
     <row r="306">
-      <c r="A306" s="4"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="5"/>
-      <c r="D306" s="5"/>
+      <c r="A306" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>349</v>
+      </c>
+      <c r="C306" s="12">
+        <v>12250.0</v>
+      </c>
+      <c r="D306" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E306" s="6"/>
       <c r="F306" s="7"/>
     </row>
     <row r="307">
-      <c r="A307" s="8"/>
-      <c r="B307" s="9"/>
-      <c r="C307" s="9"/>
-      <c r="D307" s="9"/>
+      <c r="A307" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B307" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="C307" s="39">
+        <v>510.0</v>
+      </c>
+      <c r="D307" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E307" s="10"/>
       <c r="F307" s="11"/>
     </row>
     <row r="308">
-      <c r="A308" s="4"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="5"/>
-      <c r="D308" s="5"/>
+      <c r="A308" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="C308" s="12">
+        <v>865.0</v>
+      </c>
+      <c r="D308" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E308" s="6"/>
       <c r="F308" s="7"/>
     </row>
     <row r="309">
-      <c r="A309" s="8"/>
-      <c r="B309" s="9"/>
-      <c r="C309" s="9"/>
-      <c r="D309" s="9"/>
+      <c r="A309" s="8" t="s">
+        <v>347</v>
+      </c>
+      <c r="B309" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="C309" s="39">
+        <v>20750.0</v>
+      </c>
+      <c r="D309" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E309" s="10"/>
       <c r="F309" s="11"/>
     </row>
     <row r="310">
-      <c r="A310" s="4"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="5"/>
-      <c r="D310" s="5"/>
+      <c r="A310" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="C310" s="5">
+        <v>965.0</v>
+      </c>
+      <c r="D310" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E310" s="6"/>
       <c r="F310" s="7"/>
     </row>
     <row r="311">
-      <c r="A311" s="8"/>
-      <c r="B311" s="9"/>
-      <c r="C311" s="9"/>
-      <c r="D311" s="9"/>
+      <c r="A311" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B311" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C311" s="9">
+        <v>195.0</v>
+      </c>
+      <c r="D311" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E311" s="10"/>
       <c r="F311" s="11"/>
     </row>
     <row r="312">
-      <c r="A312" s="4"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="5"/>
-      <c r="D312" s="5"/>
+      <c r="A312" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C312" s="5">
+        <v>7850.0</v>
+      </c>
+      <c r="D312" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E312" s="6"/>
       <c r="F312" s="7"/>
     </row>
     <row r="313">
-      <c r="A313" s="8"/>
-      <c r="B313" s="9"/>
-      <c r="C313" s="9"/>
-      <c r="D313" s="9"/>
+      <c r="A313" s="8" t="s">
+        <v>354</v>
+      </c>
+      <c r="B313" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C313" s="9">
+        <v>330.0</v>
+      </c>
+      <c r="D313" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E313" s="10"/>
       <c r="F313" s="11"/>
     </row>
     <row r="314">
-      <c r="A314" s="4"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="5"/>
-      <c r="D314" s="5"/>
+      <c r="A314" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C314" s="5">
+        <v>13050.0</v>
+      </c>
+      <c r="D314" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E314" s="6"/>
       <c r="F314" s="7"/>
     </row>
     <row r="315">
-      <c r="A315" s="8"/>
-      <c r="B315" s="9"/>
-      <c r="C315" s="9"/>
-      <c r="D315" s="9"/>
+      <c r="A315" s="8" t="s">
+        <v>359</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C315" s="9">
+        <v>195.0</v>
+      </c>
+      <c r="D315" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E315" s="10"/>
       <c r="F315" s="11"/>
     </row>
     <row r="316">
-      <c r="A316" s="4"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="5"/>
-      <c r="D316" s="5"/>
+      <c r="A316" s="4" t="s">
+        <v>360</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="C316" s="5">
+        <v>7800.0</v>
+      </c>
+      <c r="D316" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E316" s="6"/>
       <c r="F316" s="7"/>
     </row>
     <row r="317">
-      <c r="A317" s="8"/>
-      <c r="B317" s="9"/>
-      <c r="C317" s="9"/>
-      <c r="D317" s="9"/>
+      <c r="A317" s="8" t="s">
+        <v>360</v>
+      </c>
+      <c r="B317" s="9" t="s">
+        <v>357</v>
+      </c>
+      <c r="C317" s="9">
+        <v>330.0</v>
+      </c>
+      <c r="D317" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E317" s="10"/>
       <c r="F317" s="11"/>
     </row>
     <row r="318">
-      <c r="A318" s="4"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="5"/>
-      <c r="D318" s="5"/>
+      <c r="A318" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="C318" s="5">
+        <v>13050.0</v>
+      </c>
+      <c r="D318" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E318" s="6"/>
       <c r="F318" s="7"/>
     </row>
     <row r="319">
-      <c r="A319" s="8"/>
-      <c r="B319" s="9"/>
-      <c r="C319" s="9"/>
-      <c r="D319" s="9"/>
+      <c r="A319" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="B319" s="9" t="s">
+        <v>363</v>
+      </c>
+      <c r="C319" s="9">
+        <v>1200.0</v>
+      </c>
+      <c r="D319" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E319" s="10"/>
       <c r="F319" s="11"/>
     </row>
     <row r="320">
-      <c r="A320" s="4"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="5"/>
-      <c r="D320" s="5"/>
+      <c r="A320" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="C320" s="5">
+        <v>60000.0</v>
+      </c>
+      <c r="D320" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E320" s="6"/>
       <c r="F320" s="7"/>
     </row>
     <row r="321">
-      <c r="A321" s="8"/>
-      <c r="B321" s="9"/>
-      <c r="C321" s="9"/>
-      <c r="D321" s="9"/>
+      <c r="A321" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B321" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="C321" s="9">
+        <v>4845.0</v>
+      </c>
+      <c r="D321" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E321" s="10"/>
       <c r="F321" s="11"/>
     </row>
     <row r="322">
-      <c r="A322" s="4"/>
-      <c r="B322" s="5"/>
-      <c r="C322" s="5"/>
-      <c r="D322" s="5"/>
+      <c r="A322" s="4" t="s">
+        <v>365</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>346</v>
+      </c>
+      <c r="C322" s="5">
+        <v>12465.0</v>
+      </c>
+      <c r="D322" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E322" s="6"/>
       <c r="F322" s="7"/>
     </row>
     <row r="323">
-      <c r="A323" s="8"/>
-      <c r="B323" s="9"/>
-      <c r="C323" s="9"/>
-      <c r="D323" s="9"/>
+      <c r="A323" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B323" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="C323" s="9">
+        <v>3470.0</v>
+      </c>
+      <c r="D323" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E323" s="10"/>
       <c r="F323" s="11"/>
     </row>
     <row r="324">
-      <c r="A324" s="4"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="5"/>
-      <c r="D324" s="5"/>
+      <c r="A324" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="C324" s="5">
+        <v>4680.0</v>
+      </c>
+      <c r="D324" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E324" s="6"/>
       <c r="F324" s="7"/>
     </row>
     <row r="325">
-      <c r="A325" s="8"/>
-      <c r="B325" s="9"/>
-      <c r="C325" s="9"/>
-      <c r="D325" s="9"/>
+      <c r="A325" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B325" s="9" t="s">
+        <v>369</v>
+      </c>
+      <c r="C325" s="9">
+        <v>9360.0</v>
+      </c>
+      <c r="D325" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E325" s="10"/>
       <c r="F325" s="11"/>
     </row>
     <row r="326">
-      <c r="A326" s="4"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="5"/>
-      <c r="D326" s="5"/>
+      <c r="A326" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>371</v>
+      </c>
+      <c r="C326" s="5">
+        <v>1450.0</v>
+      </c>
+      <c r="D326" s="5" t="s">
+        <v>8</v>
+      </c>
       <c r="E326" s="6"/>
       <c r="F326" s="7"/>
     </row>
     <row r="327">
-      <c r="A327" s="8"/>
-      <c r="B327" s="9"/>
-      <c r="C327" s="9"/>
-      <c r="D327" s="9"/>
+      <c r="A327" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="B327" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="C327" s="39">
+        <v>2220.0</v>
+      </c>
+      <c r="D327" s="9" t="s">
+        <v>8</v>
+      </c>
       <c r="E327" s="10"/>
       <c r="F327" s="11"/>
     </row>
@@ -12447,12 +13762,196 @@
       <c r="F1169" s="11"/>
     </row>
     <row r="1170">
-      <c r="A1170" s="36"/>
-      <c r="B1170" s="37"/>
-      <c r="C1170" s="37"/>
-      <c r="D1170" s="37"/>
-      <c r="E1170" s="38"/>
-      <c r="F1170" s="39"/>
+      <c r="A1170" s="4"/>
+      <c r="B1170" s="5"/>
+      <c r="C1170" s="5"/>
+      <c r="D1170" s="5"/>
+      <c r="E1170" s="6"/>
+      <c r="F1170" s="7"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" s="8"/>
+      <c r="B1171" s="9"/>
+      <c r="C1171" s="9"/>
+      <c r="D1171" s="9"/>
+      <c r="E1171" s="10"/>
+      <c r="F1171" s="11"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" s="4"/>
+      <c r="B1172" s="5"/>
+      <c r="C1172" s="5"/>
+      <c r="D1172" s="5"/>
+      <c r="E1172" s="6"/>
+      <c r="F1172" s="7"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" s="8"/>
+      <c r="B1173" s="9"/>
+      <c r="C1173" s="9"/>
+      <c r="D1173" s="9"/>
+      <c r="E1173" s="10"/>
+      <c r="F1173" s="11"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" s="4"/>
+      <c r="B1174" s="5"/>
+      <c r="C1174" s="5"/>
+      <c r="D1174" s="5"/>
+      <c r="E1174" s="6"/>
+      <c r="F1174" s="7"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" s="8"/>
+      <c r="B1175" s="9"/>
+      <c r="C1175" s="9"/>
+      <c r="D1175" s="9"/>
+      <c r="E1175" s="10"/>
+      <c r="F1175" s="11"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" s="4"/>
+      <c r="B1176" s="5"/>
+      <c r="C1176" s="5"/>
+      <c r="D1176" s="5"/>
+      <c r="E1176" s="6"/>
+      <c r="F1176" s="7"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" s="8"/>
+      <c r="B1177" s="9"/>
+      <c r="C1177" s="9"/>
+      <c r="D1177" s="9"/>
+      <c r="E1177" s="10"/>
+      <c r="F1177" s="11"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" s="4"/>
+      <c r="B1178" s="5"/>
+      <c r="C1178" s="5"/>
+      <c r="D1178" s="5"/>
+      <c r="E1178" s="6"/>
+      <c r="F1178" s="7"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" s="8"/>
+      <c r="B1179" s="9"/>
+      <c r="C1179" s="9"/>
+      <c r="D1179" s="9"/>
+      <c r="E1179" s="10"/>
+      <c r="F1179" s="11"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" s="4"/>
+      <c r="B1180" s="5"/>
+      <c r="C1180" s="5"/>
+      <c r="D1180" s="5"/>
+      <c r="E1180" s="6"/>
+      <c r="F1180" s="7"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" s="8"/>
+      <c r="B1181" s="9"/>
+      <c r="C1181" s="9"/>
+      <c r="D1181" s="9"/>
+      <c r="E1181" s="10"/>
+      <c r="F1181" s="11"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" s="4"/>
+      <c r="B1182" s="5"/>
+      <c r="C1182" s="5"/>
+      <c r="D1182" s="5"/>
+      <c r="E1182" s="6"/>
+      <c r="F1182" s="7"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" s="8"/>
+      <c r="B1183" s="9"/>
+      <c r="C1183" s="9"/>
+      <c r="D1183" s="9"/>
+      <c r="E1183" s="10"/>
+      <c r="F1183" s="11"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" s="4"/>
+      <c r="B1184" s="5"/>
+      <c r="C1184" s="5"/>
+      <c r="D1184" s="5"/>
+      <c r="E1184" s="6"/>
+      <c r="F1184" s="7"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" s="8"/>
+      <c r="B1185" s="9"/>
+      <c r="C1185" s="9"/>
+      <c r="D1185" s="9"/>
+      <c r="E1185" s="10"/>
+      <c r="F1185" s="11"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" s="4"/>
+      <c r="B1186" s="5"/>
+      <c r="C1186" s="5"/>
+      <c r="D1186" s="5"/>
+      <c r="E1186" s="6"/>
+      <c r="F1186" s="7"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" s="8"/>
+      <c r="B1187" s="9"/>
+      <c r="C1187" s="9"/>
+      <c r="D1187" s="9"/>
+      <c r="E1187" s="10"/>
+      <c r="F1187" s="11"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" s="4"/>
+      <c r="B1188" s="5"/>
+      <c r="C1188" s="5"/>
+      <c r="D1188" s="5"/>
+      <c r="E1188" s="6"/>
+      <c r="F1188" s="7"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" s="8"/>
+      <c r="B1189" s="9"/>
+      <c r="C1189" s="9"/>
+      <c r="D1189" s="9"/>
+      <c r="E1189" s="10"/>
+      <c r="F1189" s="11"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" s="4"/>
+      <c r="B1190" s="5"/>
+      <c r="C1190" s="5"/>
+      <c r="D1190" s="5"/>
+      <c r="E1190" s="6"/>
+      <c r="F1190" s="7"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" s="8"/>
+      <c r="B1191" s="9"/>
+      <c r="C1191" s="9"/>
+      <c r="D1191" s="9"/>
+      <c r="E1191" s="10"/>
+      <c r="F1191" s="11"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" s="4"/>
+      <c r="B1192" s="5"/>
+      <c r="C1192" s="5"/>
+      <c r="D1192" s="5"/>
+      <c r="E1192" s="6"/>
+      <c r="F1192" s="7"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" s="48"/>
+      <c r="B1193" s="49"/>
+      <c r="C1193" s="49"/>
+      <c r="D1193" s="49"/>
+      <c r="E1193" s="50"/>
+      <c r="F1193" s="51"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
